--- a/data/calendario_promocional.xlsx
+++ b/data/calendario_promocional.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://anheuserbuschinbev-my.sharepoint.com/personal/99823517_ab-inbev_com/Documents/001. Projetos/Streamlit Calendario/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="20" documentId="11_F25DC773A252ABDACC1048AAA9DA54025ADE5901" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E79302FB-568A-405C-8E78-D417A77ADA8D}"/>
+  <xr:revisionPtr revIDLastSave="27" documentId="11_F25DC773A252ABDACC1048AAA9DA54025ADE5901" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7C01F2C6-9A9C-4CCC-8F1C-838170DF9803}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CALENDARIO" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="PRODUTOS" sheetId="3" r:id="rId3"/>
     <sheet name="CONFIG" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="162913" calcOnSave="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,12 +36,6 @@
     <t>Tipo</t>
   </si>
   <si>
-    <t>Sell In</t>
-  </si>
-  <si>
-    <t>Sell Out</t>
-  </si>
-  <si>
     <t>Regional</t>
   </si>
   <si>
@@ -136,6 +130,12 @@
   </si>
   <si>
     <t>Calendário 2.0</t>
+  </si>
+  <si>
+    <t>1ª QUINZ</t>
+  </si>
+  <si>
+    <t>2ª QUINZ</t>
   </si>
 </sst>
 </file>
@@ -179,17 +179,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -197,6 +188,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -477,52 +471,57 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="2">
+      <c r="C1" s="3"/>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="4">
         <v>46266</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="2">
+      <c r="B2" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2" s="3"/>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="4">
         <v>46267</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="2">
+      <c r="B3" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C3" s="3"/>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="4">
         <v>46280</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="2">
+      <c r="B4" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C4" s="3"/>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="4">
         <v>46281</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>3</v>
-      </c>
+      <c r="B5" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C5" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -533,37 +532,40 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D40F4A5-E774-499A-A01D-1C21EEE25028}">
   <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="31.85546875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B2" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="5" t="s">
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -575,77 +577,74 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34B2C8DF-4561-40B2-8E7C-6CD69559B9AE}">
   <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="7" width="9.140625" style="6"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="E1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F1" s="4" t="s">
+      <c r="C2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="G1" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="F2" s="5" t="s">
+      <c r="B3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="D3" s="2" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" s="5" t="s">
+      <c r="E3" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="F3" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="G3" s="2" t="s">
         <v>24</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -659,51 +658,51 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B2" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
+      <c r="B3" s="2">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B2" s="5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
+      <c r="B4" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B3" s="5">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="B5" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B6" s="2" t="s">
         <v>33</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>35</v>
       </c>
     </row>
   </sheetData>

--- a/data/calendario_promocional.xlsx
+++ b/data/calendario_promocional.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://anheuserbuschinbev-my.sharepoint.com/personal/99823517_ab-inbev_com/Documents/001. Projetos/Streamlit Calendario/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="27" documentId="11_F25DC773A252ABDACC1048AAA9DA54025ADE5901" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7C01F2C6-9A9C-4CCC-8F1C-838170DF9803}"/>
+  <xr:revisionPtr revIDLastSave="30" documentId="11_F25DC773A252ABDACC1048AAA9DA54025ADE5901" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1207953A-C329-4242-88BA-2BE787B7362D}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CALENDARIO" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="47">
   <si>
     <t>Data</t>
   </si>
@@ -78,9 +78,6 @@
     <t>Atacado</t>
   </si>
   <si>
-    <t>BC 269</t>
-  </si>
-  <si>
     <t>3.19</t>
   </si>
   <si>
@@ -93,12 +90,6 @@
     <t>Varejo</t>
   </si>
   <si>
-    <t>BC 350</t>
-  </si>
-  <si>
-    <t>3.79</t>
-  </si>
-  <si>
     <t>3.49</t>
   </si>
   <si>
@@ -136,6 +127,48 @@
   </si>
   <si>
     <t>2ª QUINZ</t>
+  </si>
+  <si>
+    <t>Quinzena</t>
+  </si>
+  <si>
+    <t>BC269</t>
+  </si>
+  <si>
+    <t>BUD269</t>
+  </si>
+  <si>
+    <t>3.39</t>
+  </si>
+  <si>
+    <t>bud269.png</t>
+  </si>
+  <si>
+    <t>BC350</t>
+  </si>
+  <si>
+    <t>MIC350</t>
+  </si>
+  <si>
+    <t>5.49</t>
+  </si>
+  <si>
+    <t>4.99</t>
+  </si>
+  <si>
+    <t>mic350.png</t>
+  </si>
+  <si>
+    <t>BRA269</t>
+  </si>
+  <si>
+    <t>3.09</t>
+  </si>
+  <si>
+    <t>2.79</t>
+  </si>
+  <si>
+    <t>bra269.png</t>
   </si>
 </sst>
 </file>
@@ -179,7 +212,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -187,7 +220,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -471,57 +503,52 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3"/>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="4">
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="3">
         <v>46266</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C2" s="3"/>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="4">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="3">
         <v>46267</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C3" s="3"/>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="4">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="3">
         <v>46280</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C4" s="3"/>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="4">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="3">
         <v>46281</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C5" s="3"/>
+        <v>32</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -575,10 +602,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34B2C8DF-4561-40B2-8E7C-6CD69559B9AE}">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>8</v>
       </c>
@@ -589,19 +616,22 @@
         <v>9</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>14</v>
       </c>
@@ -611,20 +641,23 @@
       <c r="C2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="2">
+        <v>1</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="G2" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="H2" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="G2" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>14</v>
       </c>
@@ -632,19 +665,100 @@
         <v>4</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" s="2">
+        <v>1</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="2">
+        <v>2</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="G4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H4" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>24</v>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" s="2">
+        <v>1</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="2">
+        <v>2</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -659,15 +773,15 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>14</v>
@@ -675,7 +789,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B3" s="2">
         <v>2026</v>
@@ -683,7 +797,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>4</v>
@@ -691,18 +805,18 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>

--- a/data/calendario_promocional.xlsx
+++ b/data/calendario_promocional.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://anheuserbuschinbev-my.sharepoint.com/personal/99823517_ab-inbev_com/Documents/001. Projetos/Streamlit Calendario/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="30" documentId="11_F25DC773A252ABDACC1048AAA9DA54025ADE5901" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1207953A-C329-4242-88BA-2BE787B7362D}"/>
+  <xr:revisionPtr revIDLastSave="52" documentId="11_F25DC773A252ABDACC1048AAA9DA54025ADE5901" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C7CD68AE-D82F-4717-93DC-FFA506798B5F}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CALENDARIO" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="53">
   <si>
     <t>Data</t>
   </si>
@@ -45,9 +45,6 @@
     <t>AM</t>
   </si>
   <si>
-    <t>Redes Sell In: 50% Volume do mês</t>
-  </si>
-  <si>
     <t>Core Varejo: 50% Volume do mês</t>
   </si>
   <si>
@@ -169,6 +166,27 @@
   </si>
   <si>
     <t>bra269.png</t>
+  </si>
+  <si>
+    <t>50% Volume do mês</t>
+  </si>
+  <si>
+    <t>Sell in</t>
+  </si>
+  <si>
+    <t>Mês</t>
+  </si>
+  <si>
+    <t>Sell out</t>
+  </si>
+  <si>
+    <t>30% Volume do mês</t>
+  </si>
+  <si>
+    <t>Core Varejo: 10% Volume do mês</t>
+  </si>
+  <si>
+    <t>Core Cash: 20 R$/HL</t>
   </si>
 </sst>
 </file>
@@ -523,7 +541,7 @@
         <v>46266</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -531,7 +549,7 @@
         <v>46267</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -539,7 +557,7 @@
         <v>46280</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -547,7 +565,7 @@
         <v>46281</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -557,42 +575,87 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D40F4A5-E774-499A-A01D-1C21EEE25028}">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="31.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="31.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>2</v>
+        <v>48</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="2" t="s">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>7</v>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -607,158 +670,158 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>4</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D2" s="2">
         <v>1</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="H2" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>4</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D3" s="2">
         <v>1</v>
       </c>
       <c r="E3" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="G3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H3" s="2" t="s">
         <v>36</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>4</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D4" s="2">
         <v>2</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F4" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H4" s="2" t="s">
         <v>20</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>4</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D5" s="2">
         <v>1</v>
       </c>
       <c r="E5" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="G5" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="H5" s="2" t="s">
         <v>41</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>4</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D6" s="2">
         <v>2</v>
       </c>
       <c r="E6" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="G6" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="H6" s="2" t="s">
         <v>45</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -773,23 +836,23 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B3" s="2">
         <v>2026</v>
@@ -797,7 +860,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>4</v>
@@ -805,18 +868,18 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>27</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>29</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>30</v>
       </c>
     </row>
   </sheetData>

--- a/data/calendario_promocional.xlsx
+++ b/data/calendario_promocional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://anheuserbuschinbev-my.sharepoint.com/personal/99823517_ab-inbev_com/Documents/001. Projetos/Streamlit Calendario/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="52" documentId="11_F25DC773A252ABDACC1048AAA9DA54025ADE5901" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C7CD68AE-D82F-4717-93DC-FFA506798B5F}"/>
+  <xr:revisionPtr revIDLastSave="53" documentId="11_F25DC773A252ABDACC1048AAA9DA54025ADE5901" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F39F218A-B34B-4C66-B77F-9F831B95505B}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="52">
   <si>
     <t>Data</t>
   </si>
@@ -172,9 +172,6 @@
   </si>
   <si>
     <t>Sell in</t>
-  </si>
-  <si>
-    <t>Mês</t>
   </si>
   <si>
     <t>Sell out</t>
@@ -583,7 +580,7 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>48</v>
+        <v>7</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -630,10 +627,10 @@
         <v>13</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>49</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -641,10 +638,10 @@
         <v>13</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -652,10 +649,10 @@
         <v>13</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>

--- a/data/calendario_promocional.xlsx
+++ b/data/calendario_promocional.xlsx
@@ -8,27 +8,42 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://anheuserbuschinbev-my.sharepoint.com/personal/99823517_ab-inbev_com/Documents/001. Projetos/Streamlit Calendario/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="53" documentId="11_F25DC773A252ABDACC1048AAA9DA54025ADE5901" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F39F218A-B34B-4C66-B77F-9F831B95505B}"/>
+  <xr:revisionPtr revIDLastSave="157" documentId="11_F25DC773A252ABDACC1048AAA9DA54025ADE5901" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AD2DA07D-C33E-41E1-BBE4-814A1D1B5B96}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="CALENDARIO" sheetId="1" r:id="rId1"/>
-    <sheet name="MECANICA" sheetId="2" r:id="rId2"/>
-    <sheet name="PRODUTOS" sheetId="3" r:id="rId3"/>
-    <sheet name="CONFIG" sheetId="4" r:id="rId4"/>
+    <sheet name="DeparaIMG" sheetId="5" r:id="rId1"/>
+    <sheet name="CALENDARIO" sheetId="1" r:id="rId2"/>
+    <sheet name="MECANICA" sheetId="2" r:id="rId3"/>
+    <sheet name="PRODUTOS" sheetId="3" r:id="rId4"/>
+    <sheet name="CONFIG" sheetId="4" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="162913" calcOnSave="0"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">PRODUTOS!$A$1:$H$75</definedName>
+  </definedNames>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="65">
   <si>
     <t>Data</t>
   </si>
@@ -45,12 +60,6 @@
     <t>AM</t>
   </si>
   <si>
-    <t>Core Varejo: 50% Volume do mês</t>
-  </si>
-  <si>
-    <t>Core Cash: 60 R$/HL</t>
-  </si>
-  <si>
     <t>Mes</t>
   </si>
   <si>
@@ -72,27 +81,6 @@
     <t>Setembro</t>
   </si>
   <si>
-    <t>Atacado</t>
-  </si>
-  <si>
-    <t>3.19</t>
-  </si>
-  <si>
-    <t>2.99</t>
-  </si>
-  <si>
-    <t>bc269.png</t>
-  </si>
-  <si>
-    <t>Varejo</t>
-  </si>
-  <si>
-    <t>3.49</t>
-  </si>
-  <si>
-    <t>bc350.png</t>
-  </si>
-  <si>
     <t>Chave</t>
   </si>
   <si>
@@ -129,61 +117,127 @@
     <t>Quinzena</t>
   </si>
   <si>
-    <t>BC269</t>
-  </si>
-  <si>
-    <t>BUD269</t>
-  </si>
-  <si>
-    <t>3.39</t>
-  </si>
-  <si>
-    <t>bud269.png</t>
-  </si>
-  <si>
-    <t>BC350</t>
-  </si>
-  <si>
-    <t>MIC350</t>
-  </si>
-  <si>
-    <t>5.49</t>
-  </si>
-  <si>
-    <t>4.99</t>
-  </si>
-  <si>
-    <t>mic350.png</t>
-  </si>
-  <si>
-    <t>BRA269</t>
-  </si>
-  <si>
-    <t>3.09</t>
-  </si>
-  <si>
-    <t>2.79</t>
-  </si>
-  <si>
-    <t>bra269.png</t>
-  </si>
-  <si>
-    <t>50% Volume do mês</t>
-  </si>
-  <si>
     <t>Sell in</t>
   </si>
   <si>
     <t>Sell out</t>
   </si>
   <si>
-    <t>30% Volume do mês</t>
-  </si>
-  <si>
-    <t>Core Varejo: 10% Volume do mês</t>
-  </si>
-  <si>
-    <t>Core Cash: 20 R$/HL</t>
+    <t>1Q</t>
+  </si>
+  <si>
+    <t>2Q</t>
+  </si>
+  <si>
+    <t>ATACADO</t>
+  </si>
+  <si>
+    <t>VAREJO</t>
+  </si>
+  <si>
+    <t>RR/AC</t>
+  </si>
+  <si>
+    <t>DF</t>
+  </si>
+  <si>
+    <t>GO</t>
+  </si>
+  <si>
+    <t>TO/MT/MS</t>
+  </si>
+  <si>
+    <t>GCA P1</t>
+  </si>
+  <si>
+    <t>GCA P1,5</t>
+  </si>
+  <si>
+    <t>PC P2</t>
+  </si>
+  <si>
+    <t>BARE P2</t>
+  </si>
+  <si>
+    <t>H2OH P500</t>
+  </si>
+  <si>
+    <t>SUK P2</t>
+  </si>
+  <si>
+    <t>GCA P2</t>
+  </si>
+  <si>
+    <t>GCA LT350</t>
+  </si>
+  <si>
+    <t>PCB LT350</t>
+  </si>
+  <si>
+    <t>GCA LT269</t>
+  </si>
+  <si>
+    <t>PC LT269</t>
+  </si>
+  <si>
+    <t>H2OH P1,5</t>
+  </si>
+  <si>
+    <t>GCAP1</t>
+  </si>
+  <si>
+    <t>PCP2</t>
+  </si>
+  <si>
+    <t>BAREP2</t>
+  </si>
+  <si>
+    <t>SUKP2</t>
+  </si>
+  <si>
+    <t>GCAP2</t>
+  </si>
+  <si>
+    <t>GCAP1,5</t>
+  </si>
+  <si>
+    <t>H2OHP500</t>
+  </si>
+  <si>
+    <t>GCA350</t>
+  </si>
+  <si>
+    <t>GCA269</t>
+  </si>
+  <si>
+    <t>PC269</t>
+  </si>
+  <si>
+    <t>PCB350</t>
+  </si>
+  <si>
+    <t>H2OHP1,5</t>
+  </si>
+  <si>
+    <t>Nome IMG</t>
+  </si>
+  <si>
+    <t>Caminho</t>
+  </si>
+  <si>
+    <t>Ativação: Quinzenal</t>
+  </si>
+  <si>
+    <t>Apuração Varejo: Pagamento 60% do Sell In no Mês</t>
+  </si>
+  <si>
+    <t>Negociação: Sell In e Sell Out</t>
+  </si>
+  <si>
+    <t>Apuração Cash: Pagamento 100% do Sell In no Mês</t>
+  </si>
+  <si>
+    <t>Apuração Varejo: 100% no períiodo, com check de TTC</t>
   </si>
 </sst>
 </file>
@@ -242,7 +296,18 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -517,8 +582,181 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0BF5819-473C-445D-A53D-FC51ACB237C6}">
+  <dimension ref="A1:C13"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2" t="str">
+        <f>B2&amp;".png"</f>
+        <v>GCAP1.png</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C3" t="str">
+        <f t="shared" ref="C3:C13" si="0">B3&amp;".png"</f>
+        <v>GCAP1,5.png</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C4" t="str">
+        <f t="shared" si="0"/>
+        <v>PCP2.png</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B5" t="s">
+        <v>48</v>
+      </c>
+      <c r="C5" t="str">
+        <f t="shared" si="0"/>
+        <v>BAREP2.png</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C6" t="str">
+        <f t="shared" si="0"/>
+        <v>H2OHP500.png</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B7" t="s">
+        <v>49</v>
+      </c>
+      <c r="C7" t="str">
+        <f t="shared" si="0"/>
+        <v>SUKP2.png</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>40</v>
+      </c>
+      <c r="B8" t="s">
+        <v>50</v>
+      </c>
+      <c r="C8" t="str">
+        <f t="shared" si="0"/>
+        <v>GCAP2.png</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>41</v>
+      </c>
+      <c r="B9" t="s">
+        <v>53</v>
+      </c>
+      <c r="C9" t="str">
+        <f t="shared" si="0"/>
+        <v>GCA350.png</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>42</v>
+      </c>
+      <c r="B10" t="s">
+        <v>56</v>
+      </c>
+      <c r="C10" t="str">
+        <f t="shared" si="0"/>
+        <v>PCB350.png</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>43</v>
+      </c>
+      <c r="B11" t="s">
+        <v>54</v>
+      </c>
+      <c r="C11" t="str">
+        <f t="shared" si="0"/>
+        <v>GCA269.png</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>44</v>
+      </c>
+      <c r="B12" t="s">
+        <v>55</v>
+      </c>
+      <c r="C12" t="str">
+        <f t="shared" si="0"/>
+        <v>PC269.png</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>45</v>
+      </c>
+      <c r="B13" t="s">
+        <v>57</v>
+      </c>
+      <c r="C13" t="str">
+        <f t="shared" si="0"/>
+        <v>H2OHP1,5.png</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="B1:B1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B35"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
@@ -538,31 +776,304 @@
         <v>46266</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
+        <f>A2+1</f>
         <v>46267</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
-        <v>46280</v>
+        <f t="shared" ref="A4:A35" si="0">A3+1</f>
+        <v>46268</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
+        <f t="shared" si="0"/>
+        <v>46269</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="3">
+        <f t="shared" si="0"/>
+        <v>46270</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="3">
+        <f t="shared" si="0"/>
+        <v>46271</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="3">
+        <f t="shared" si="0"/>
+        <v>46272</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="3">
+        <f t="shared" si="0"/>
+        <v>46273</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="3">
+        <f t="shared" si="0"/>
+        <v>46274</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="3">
+        <f t="shared" si="0"/>
+        <v>46275</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="3">
+        <f t="shared" si="0"/>
+        <v>46276</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="3">
+        <f t="shared" si="0"/>
+        <v>46277</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="3">
+        <f t="shared" si="0"/>
+        <v>46278</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="3">
+        <f t="shared" si="0"/>
+        <v>46279</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="3">
+        <f t="shared" si="0"/>
+        <v>46280</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="3">
+        <f t="shared" si="0"/>
         <v>46281</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>31</v>
+      <c r="B17" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="3">
+        <f t="shared" si="0"/>
+        <v>46282</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="3">
+        <f t="shared" si="0"/>
+        <v>46283</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="3">
+        <f t="shared" si="0"/>
+        <v>46284</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" s="3">
+        <f t="shared" si="0"/>
+        <v>46285</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="3">
+        <f t="shared" si="0"/>
+        <v>46286</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" s="3">
+        <f t="shared" si="0"/>
+        <v>46287</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" s="3">
+        <f t="shared" si="0"/>
+        <v>46288</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" s="3">
+        <f t="shared" si="0"/>
+        <v>46289</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" s="3">
+        <f t="shared" si="0"/>
+        <v>46290</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" s="3">
+        <f t="shared" si="0"/>
+        <v>46291</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" s="3">
+        <f t="shared" si="0"/>
+        <v>46292</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" s="3">
+        <f t="shared" si="0"/>
+        <v>46293</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" s="3">
+        <f t="shared" si="0"/>
+        <v>46294</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" s="3">
+        <f t="shared" si="0"/>
+        <v>46295</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" s="3">
+        <f t="shared" si="0"/>
+        <v>46296</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" s="3">
+        <f t="shared" si="0"/>
+        <v>46297</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" s="3">
+        <f t="shared" si="0"/>
+        <v>46298</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" s="3">
+        <f t="shared" si="0"/>
+        <v>46299</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -570,17 +1081,17 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D40F4A5-E774-499A-A01D-1C21EEE25028}">
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="31.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="47.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -591,234 +1102,79 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>46</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>5</v>
+        <v>62</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>6</v>
+        <v>61</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34B2C8DF-4561-40B2-8E7C-6CD69559B9AE}">
-  <dimension ref="A1:H6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D2" s="2">
-        <v>1</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" s="2">
-        <v>1</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" s="2">
-        <v>2</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D5" s="2">
-        <v>1</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D6" s="2">
-        <v>2</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>45</v>
+        <v>62</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -827,29 +1183,2070 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34B2C8DF-4561-40B2-8E7C-6CD69559B9AE}">
+  <dimension ref="A1:H76"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="8" max="8" width="14.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F2" s="2">
+        <v>4.99</v>
+      </c>
+      <c r="G2" s="2">
+        <v>4.6900000000000004</v>
+      </c>
+      <c r="H2" s="2" t="str">
+        <f>_xlfn.XLOOKUP(E2,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
+        <v>GCAP1.png</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="F3" s="2">
+        <v>6.49</v>
+      </c>
+      <c r="G3" s="2">
+        <v>6.19</v>
+      </c>
+      <c r="H3" s="2" t="str">
+        <f>_xlfn.XLOOKUP(E3,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
+        <v>GCAP1,5.png</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="F4" s="2">
+        <v>6.49</v>
+      </c>
+      <c r="G4" s="2">
+        <v>6.19</v>
+      </c>
+      <c r="H4" s="2" t="str">
+        <f>_xlfn.XLOOKUP(E4,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
+        <v>GCAP1,5.png</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="F5" s="2">
+        <v>6.49</v>
+      </c>
+      <c r="G5" s="2">
+        <v>6.19</v>
+      </c>
+      <c r="H5" s="2" t="str">
+        <f>_xlfn.XLOOKUP(E5,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
+        <v>GCAP1,5.png</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="F6" s="2">
+        <v>6.49</v>
+      </c>
+      <c r="G6" s="2">
+        <v>6.19</v>
+      </c>
+      <c r="H6" s="2" t="str">
+        <f>_xlfn.XLOOKUP(E6,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
+        <v>GCAP1,5.png</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E7" t="s">
+        <v>36</v>
+      </c>
+      <c r="F7">
+        <v>7.79</v>
+      </c>
+      <c r="G7">
+        <v>7.29</v>
+      </c>
+      <c r="H7" s="2" t="str">
+        <f>_xlfn.XLOOKUP(E7,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
+        <v>PCP2.png</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" t="s">
+        <v>28</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E8" t="s">
+        <v>36</v>
+      </c>
+      <c r="F8">
+        <v>8.49</v>
+      </c>
+      <c r="G8">
+        <v>7.99</v>
+      </c>
+      <c r="H8" s="2" t="str">
+        <f>_xlfn.XLOOKUP(E8,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
+        <v>PCP2.png</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9" t="s">
+        <v>28</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F9">
+        <v>7.49</v>
+      </c>
+      <c r="G9">
+        <v>6.99</v>
+      </c>
+      <c r="H9" s="2" t="str">
+        <f>_xlfn.XLOOKUP(E9,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
+        <v>PCP2.png</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10" t="s">
+        <v>28</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E10" t="s">
+        <v>36</v>
+      </c>
+      <c r="F10">
+        <v>7.49</v>
+      </c>
+      <c r="G10">
+        <v>6.99</v>
+      </c>
+      <c r="H10" s="2" t="str">
+        <f>_xlfn.XLOOKUP(E10,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
+        <v>PCP2.png</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" t="s">
+        <v>33</v>
+      </c>
+      <c r="C11" t="s">
+        <v>28</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E11" t="s">
+        <v>36</v>
+      </c>
+      <c r="F11">
+        <v>8.49</v>
+      </c>
+      <c r="G11">
+        <v>7.99</v>
+      </c>
+      <c r="H11" s="2" t="str">
+        <f>_xlfn.XLOOKUP(E11,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
+        <v>PCP2.png</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>4</v>
+      </c>
+      <c r="C12" t="s">
+        <v>28</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E12" t="s">
+        <v>37</v>
+      </c>
+      <c r="F12">
+        <v>5.49</v>
+      </c>
+      <c r="G12">
+        <v>5.19</v>
+      </c>
+      <c r="H12" s="2" t="str">
+        <f>_xlfn.XLOOKUP(E12,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
+        <v>BAREP2.png</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" t="s">
+        <v>30</v>
+      </c>
+      <c r="C13" t="s">
+        <v>28</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E13" t="s">
+        <v>38</v>
+      </c>
+      <c r="F13">
+        <v>5.29</v>
+      </c>
+      <c r="G13">
+        <v>4.99</v>
+      </c>
+      <c r="H13" s="2" t="str">
+        <f>_xlfn.XLOOKUP(E13,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
+        <v>H2OHP500.png</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B14" t="s">
+        <v>31</v>
+      </c>
+      <c r="C14" t="s">
+        <v>28</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E14" t="s">
+        <v>38</v>
+      </c>
+      <c r="F14">
+        <v>5.29</v>
+      </c>
+      <c r="G14">
+        <v>4.99</v>
+      </c>
+      <c r="H14" s="2" t="str">
+        <f>_xlfn.XLOOKUP(E14,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
+        <v>H2OHP500.png</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B15" t="s">
+        <v>32</v>
+      </c>
+      <c r="C15" t="s">
+        <v>28</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E15" t="s">
+        <v>38</v>
+      </c>
+      <c r="F15">
+        <v>5.29</v>
+      </c>
+      <c r="G15">
+        <v>4.99</v>
+      </c>
+      <c r="H15" s="2" t="str">
+        <f>_xlfn.XLOOKUP(E15,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
+        <v>H2OHP500.png</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B16" t="s">
+        <v>33</v>
+      </c>
+      <c r="C16" t="s">
+        <v>28</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E16" t="s">
+        <v>38</v>
+      </c>
+      <c r="F16">
+        <v>5.29</v>
+      </c>
+      <c r="G16">
+        <v>4.99</v>
+      </c>
+      <c r="H16" s="2" t="str">
+        <f>_xlfn.XLOOKUP(E16,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
+        <v>H2OHP500.png</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B17" t="s">
+        <v>4</v>
+      </c>
+      <c r="C17" t="s">
+        <v>28</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E17" t="s">
+        <v>39</v>
+      </c>
+      <c r="F17">
+        <v>6.79</v>
+      </c>
+      <c r="G17">
+        <v>6.29</v>
+      </c>
+      <c r="H17" s="2" t="str">
+        <f>_xlfn.XLOOKUP(E17,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
+        <v>SUKP2.png</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B18" t="s">
+        <v>30</v>
+      </c>
+      <c r="C18" t="s">
+        <v>28</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E18" t="s">
+        <v>39</v>
+      </c>
+      <c r="F18">
+        <v>6.79</v>
+      </c>
+      <c r="G18">
+        <v>6.29</v>
+      </c>
+      <c r="H18" s="2" t="str">
+        <f>_xlfn.XLOOKUP(E18,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
+        <v>SUKP2.png</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B19" t="s">
+        <v>31</v>
+      </c>
+      <c r="C19" t="s">
+        <v>28</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E19" t="s">
+        <v>39</v>
+      </c>
+      <c r="F19">
+        <v>6.79</v>
+      </c>
+      <c r="G19">
+        <v>6.29</v>
+      </c>
+      <c r="H19" s="2" t="str">
+        <f>_xlfn.XLOOKUP(E19,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
+        <v>SUKP2.png</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B20" t="s">
+        <v>32</v>
+      </c>
+      <c r="C20" t="s">
+        <v>28</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E20" t="s">
+        <v>39</v>
+      </c>
+      <c r="F20">
+        <v>6.79</v>
+      </c>
+      <c r="G20">
+        <v>6.29</v>
+      </c>
+      <c r="H20" s="2" t="str">
+        <f>_xlfn.XLOOKUP(E20,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
+        <v>SUKP2.png</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B21" t="s">
+        <v>33</v>
+      </c>
+      <c r="C21" t="s">
+        <v>28</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E21" t="s">
+        <v>39</v>
+      </c>
+      <c r="F21">
+        <v>7.29</v>
+      </c>
+      <c r="G21">
+        <v>6.79</v>
+      </c>
+      <c r="H21" s="2" t="str">
+        <f>_xlfn.XLOOKUP(E21,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
+        <v>SUKP2.png</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B22" t="s">
+        <v>4</v>
+      </c>
+      <c r="C22" t="s">
+        <v>29</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E22" t="s">
+        <v>40</v>
+      </c>
+      <c r="F22">
+        <v>8.99</v>
+      </c>
+      <c r="G22">
+        <v>8.49</v>
+      </c>
+      <c r="H22" s="2" t="str">
+        <f>_xlfn.XLOOKUP(E22,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
+        <v>GCAP2.png</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B23" t="s">
+        <v>30</v>
+      </c>
+      <c r="C23" t="s">
+        <v>29</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E23" t="s">
+        <v>40</v>
+      </c>
+      <c r="F23">
+        <v>8.99</v>
+      </c>
+      <c r="G23">
+        <v>8.49</v>
+      </c>
+      <c r="H23" s="2" t="str">
+        <f>_xlfn.XLOOKUP(E23,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
+        <v>GCAP2.png</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B24" t="s">
+        <v>31</v>
+      </c>
+      <c r="C24" t="s">
+        <v>29</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E24" t="s">
+        <v>40</v>
+      </c>
+      <c r="F24">
+        <v>8.2899999999999991</v>
+      </c>
+      <c r="G24">
+        <v>7.7899999999999991</v>
+      </c>
+      <c r="H24" s="2" t="str">
+        <f>_xlfn.XLOOKUP(E24,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
+        <v>GCAP2.png</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B25" t="s">
+        <v>32</v>
+      </c>
+      <c r="C25" t="s">
+        <v>29</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E25" t="s">
+        <v>40</v>
+      </c>
+      <c r="F25">
+        <v>8.2899999999999991</v>
+      </c>
+      <c r="G25">
+        <v>7.7899999999999991</v>
+      </c>
+      <c r="H25" s="2" t="str">
+        <f>_xlfn.XLOOKUP(E25,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
+        <v>GCAP2.png</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B26" t="s">
+        <v>33</v>
+      </c>
+      <c r="C26" t="s">
+        <v>29</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E26" t="s">
+        <v>40</v>
+      </c>
+      <c r="F26">
+        <v>9.49</v>
+      </c>
+      <c r="G26">
+        <v>8.99</v>
+      </c>
+      <c r="H26" s="2" t="str">
+        <f>_xlfn.XLOOKUP(E26,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
+        <v>GCAP2.png</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B27" t="s">
+        <v>4</v>
+      </c>
+      <c r="C27" t="s">
+        <v>29</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E27" t="s">
+        <v>41</v>
+      </c>
+      <c r="F27">
+        <v>3.49</v>
+      </c>
+      <c r="G27">
+        <v>3.1900000000000004</v>
+      </c>
+      <c r="H27" s="2" t="str">
+        <f>_xlfn.XLOOKUP(E27,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
+        <v>GCA350.png</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B28" t="s">
+        <v>30</v>
+      </c>
+      <c r="C28" t="s">
+        <v>29</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E28" t="s">
+        <v>41</v>
+      </c>
+      <c r="F28">
+        <v>3.49</v>
+      </c>
+      <c r="G28">
+        <v>3.1900000000000004</v>
+      </c>
+      <c r="H28" s="2" t="str">
+        <f>_xlfn.XLOOKUP(E28,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
+        <v>GCA350.png</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B29" t="s">
+        <v>31</v>
+      </c>
+      <c r="C29" t="s">
+        <v>29</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E29" t="s">
+        <v>41</v>
+      </c>
+      <c r="F29">
+        <v>3.49</v>
+      </c>
+      <c r="G29">
+        <v>3.1900000000000004</v>
+      </c>
+      <c r="H29" s="2" t="str">
+        <f>_xlfn.XLOOKUP(E29,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
+        <v>GCA350.png</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B30" t="s">
+        <v>32</v>
+      </c>
+      <c r="C30" t="s">
+        <v>29</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E30" t="s">
+        <v>41</v>
+      </c>
+      <c r="F30">
+        <v>3.49</v>
+      </c>
+      <c r="G30">
+        <v>3.1900000000000004</v>
+      </c>
+      <c r="H30" s="2" t="str">
+        <f>_xlfn.XLOOKUP(E30,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
+        <v>GCA350.png</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B31" t="s">
+        <v>33</v>
+      </c>
+      <c r="C31" t="s">
+        <v>29</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E31" t="s">
+        <v>41</v>
+      </c>
+      <c r="F31">
+        <v>3.49</v>
+      </c>
+      <c r="G31">
+        <v>3.1900000000000004</v>
+      </c>
+      <c r="H31" s="2" t="str">
+        <f>_xlfn.XLOOKUP(E31,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
+        <v>GCA350.png</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B32" t="s">
+        <v>4</v>
+      </c>
+      <c r="C32" t="s">
+        <v>29</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E32" t="s">
+        <v>37</v>
+      </c>
+      <c r="F32">
+        <v>5.69</v>
+      </c>
+      <c r="G32">
+        <v>5.19</v>
+      </c>
+      <c r="H32" s="2" t="str">
+        <f>_xlfn.XLOOKUP(E32,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
+        <v>BAREP2.png</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B33" t="s">
+        <v>30</v>
+      </c>
+      <c r="C33" t="s">
+        <v>29</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E33" t="s">
+        <v>38</v>
+      </c>
+      <c r="F33">
+        <v>5.49</v>
+      </c>
+      <c r="G33">
+        <v>5.19</v>
+      </c>
+      <c r="H33" s="2" t="str">
+        <f>_xlfn.XLOOKUP(E33,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
+        <v>H2OHP500.png</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B34" t="s">
+        <v>31</v>
+      </c>
+      <c r="C34" t="s">
+        <v>29</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E34" t="s">
+        <v>38</v>
+      </c>
+      <c r="F34">
+        <v>5.49</v>
+      </c>
+      <c r="G34">
+        <v>5.19</v>
+      </c>
+      <c r="H34" s="2" t="str">
+        <f>_xlfn.XLOOKUP(E34,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
+        <v>H2OHP500.png</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B35" t="s">
+        <v>32</v>
+      </c>
+      <c r="C35" t="s">
+        <v>29</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E35" t="s">
+        <v>38</v>
+      </c>
+      <c r="F35">
+        <v>5.49</v>
+      </c>
+      <c r="G35">
+        <v>5.19</v>
+      </c>
+      <c r="H35" s="2" t="str">
+        <f>_xlfn.XLOOKUP(E35,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
+        <v>H2OHP500.png</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B36" t="s">
+        <v>33</v>
+      </c>
+      <c r="C36" t="s">
+        <v>29</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E36" t="s">
+        <v>38</v>
+      </c>
+      <c r="F36">
+        <v>5.49</v>
+      </c>
+      <c r="G36">
+        <v>5.19</v>
+      </c>
+      <c r="H36" s="2" t="str">
+        <f>_xlfn.XLOOKUP(E36,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
+        <v>H2OHP500.png</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B37" t="s">
+        <v>4</v>
+      </c>
+      <c r="C37" t="s">
+        <v>29</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E37" t="s">
+        <v>42</v>
+      </c>
+      <c r="F37">
+        <v>3.39</v>
+      </c>
+      <c r="G37">
+        <v>2.99</v>
+      </c>
+      <c r="H37" s="2" t="str">
+        <f>_xlfn.XLOOKUP(E37,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
+        <v>PCB350.png</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B38" t="s">
+        <v>30</v>
+      </c>
+      <c r="C38" t="s">
+        <v>29</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E38" t="s">
+        <v>42</v>
+      </c>
+      <c r="F38">
+        <v>3.39</v>
+      </c>
+      <c r="G38">
+        <v>2.99</v>
+      </c>
+      <c r="H38" s="2" t="str">
+        <f>_xlfn.XLOOKUP(E38,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
+        <v>PCB350.png</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B39" t="s">
+        <v>31</v>
+      </c>
+      <c r="C39" t="s">
+        <v>29</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E39" t="s">
+        <v>42</v>
+      </c>
+      <c r="F39">
+        <v>3.39</v>
+      </c>
+      <c r="G39">
+        <v>2.99</v>
+      </c>
+      <c r="H39" s="2" t="str">
+        <f>_xlfn.XLOOKUP(E39,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
+        <v>PCB350.png</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B40" t="s">
+        <v>32</v>
+      </c>
+      <c r="C40" t="s">
+        <v>29</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E40" t="s">
+        <v>42</v>
+      </c>
+      <c r="F40">
+        <v>3.39</v>
+      </c>
+      <c r="G40">
+        <v>2.99</v>
+      </c>
+      <c r="H40" s="2" t="str">
+        <f>_xlfn.XLOOKUP(E40,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
+        <v>PCB350.png</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B41" t="s">
+        <v>33</v>
+      </c>
+      <c r="C41" t="s">
+        <v>29</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E41" t="s">
+        <v>42</v>
+      </c>
+      <c r="F41">
+        <v>3.39</v>
+      </c>
+      <c r="G41">
+        <v>2.99</v>
+      </c>
+      <c r="H41" s="2" t="str">
+        <f>_xlfn.XLOOKUP(E41,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
+        <v>PCB350.png</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B42" t="s">
+        <v>4</v>
+      </c>
+      <c r="C42" t="s">
+        <v>28</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E42" t="s">
+        <v>40</v>
+      </c>
+      <c r="F42">
+        <v>8.7899999999999991</v>
+      </c>
+      <c r="G42">
+        <v>8.2899999999999991</v>
+      </c>
+      <c r="H42" s="2" t="str">
+        <f>_xlfn.XLOOKUP(E42,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
+        <v>GCAP2.png</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B43" t="s">
+        <v>30</v>
+      </c>
+      <c r="C43" t="s">
+        <v>28</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E43" t="s">
+        <v>40</v>
+      </c>
+      <c r="F43">
+        <v>8.7899999999999991</v>
+      </c>
+      <c r="G43">
+        <v>8.2899999999999991</v>
+      </c>
+      <c r="H43" s="2" t="str">
+        <f>_xlfn.XLOOKUP(E43,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
+        <v>GCAP2.png</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B44" t="s">
+        <v>31</v>
+      </c>
+      <c r="C44" t="s">
+        <v>28</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E44" t="s">
+        <v>40</v>
+      </c>
+      <c r="F44">
+        <v>7.99</v>
+      </c>
+      <c r="G44">
+        <v>7.49</v>
+      </c>
+      <c r="H44" s="2" t="str">
+        <f>_xlfn.XLOOKUP(E44,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
+        <v>GCAP2.png</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B45" t="s">
+        <v>32</v>
+      </c>
+      <c r="C45" t="s">
+        <v>28</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E45" t="s">
+        <v>40</v>
+      </c>
+      <c r="F45">
+        <v>7.99</v>
+      </c>
+      <c r="G45">
+        <v>7.49</v>
+      </c>
+      <c r="H45" s="2" t="str">
+        <f>_xlfn.XLOOKUP(E45,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
+        <v>GCAP2.png</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B46" t="s">
+        <v>33</v>
+      </c>
+      <c r="C46" t="s">
+        <v>28</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E46" t="s">
+        <v>40</v>
+      </c>
+      <c r="F46">
+        <v>9.2899999999999991</v>
+      </c>
+      <c r="G46">
+        <v>8.7899999999999991</v>
+      </c>
+      <c r="H46" s="2" t="str">
+        <f>_xlfn.XLOOKUP(E46,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
+        <v>GCAP2.png</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B47" t="s">
+        <v>4</v>
+      </c>
+      <c r="C47" t="s">
+        <v>28</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E47" t="s">
+        <v>43</v>
+      </c>
+      <c r="F47">
+        <v>2.39</v>
+      </c>
+      <c r="G47">
+        <v>2.19</v>
+      </c>
+      <c r="H47" s="2" t="str">
+        <f>_xlfn.XLOOKUP(E47,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
+        <v>GCA269.png</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B48" t="s">
+        <v>30</v>
+      </c>
+      <c r="C48" t="s">
+        <v>28</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E48" t="s">
+        <v>43</v>
+      </c>
+      <c r="F48">
+        <v>2.39</v>
+      </c>
+      <c r="G48">
+        <v>2.19</v>
+      </c>
+      <c r="H48" s="2" t="str">
+        <f>_xlfn.XLOOKUP(E48,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
+        <v>GCA269.png</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B49" t="s">
+        <v>31</v>
+      </c>
+      <c r="C49" t="s">
+        <v>28</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E49" t="s">
+        <v>43</v>
+      </c>
+      <c r="F49">
+        <v>2.39</v>
+      </c>
+      <c r="G49">
+        <v>2.19</v>
+      </c>
+      <c r="H49" s="2" t="str">
+        <f>_xlfn.XLOOKUP(E49,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
+        <v>GCA269.png</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B50" t="s">
+        <v>32</v>
+      </c>
+      <c r="C50" t="s">
+        <v>28</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E50" t="s">
+        <v>43</v>
+      </c>
+      <c r="F50">
+        <v>2.39</v>
+      </c>
+      <c r="G50">
+        <v>2.19</v>
+      </c>
+      <c r="H50" s="2" t="str">
+        <f>_xlfn.XLOOKUP(E50,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
+        <v>GCA269.png</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B51" t="s">
+        <v>33</v>
+      </c>
+      <c r="C51" t="s">
+        <v>28</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E51" t="s">
+        <v>43</v>
+      </c>
+      <c r="F51">
+        <v>2.39</v>
+      </c>
+      <c r="G51">
+        <v>2.19</v>
+      </c>
+      <c r="H51" s="2" t="str">
+        <f>_xlfn.XLOOKUP(E51,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
+        <v>GCA269.png</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B52" t="s">
+        <v>4</v>
+      </c>
+      <c r="C52" t="s">
+        <v>28</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E52" t="s">
+        <v>44</v>
+      </c>
+      <c r="F52">
+        <v>2.29</v>
+      </c>
+      <c r="G52">
+        <v>2.09</v>
+      </c>
+      <c r="H52" s="2" t="str">
+        <f>_xlfn.XLOOKUP(E52,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
+        <v>PC269.png</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B53" t="s">
+        <v>30</v>
+      </c>
+      <c r="C53" t="s">
+        <v>28</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E53" t="s">
+        <v>44</v>
+      </c>
+      <c r="F53">
+        <v>2.29</v>
+      </c>
+      <c r="G53">
+        <v>2.09</v>
+      </c>
+      <c r="H53" s="2" t="str">
+        <f>_xlfn.XLOOKUP(E53,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
+        <v>PC269.png</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B54" t="s">
+        <v>31</v>
+      </c>
+      <c r="C54" t="s">
+        <v>28</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E54" t="s">
+        <v>44</v>
+      </c>
+      <c r="F54">
+        <v>2.29</v>
+      </c>
+      <c r="G54">
+        <v>2.09</v>
+      </c>
+      <c r="H54" s="2" t="str">
+        <f>_xlfn.XLOOKUP(E54,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
+        <v>PC269.png</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B55" t="s">
+        <v>32</v>
+      </c>
+      <c r="C55" t="s">
+        <v>28</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E55" t="s">
+        <v>44</v>
+      </c>
+      <c r="F55">
+        <v>2.29</v>
+      </c>
+      <c r="G55">
+        <v>2.09</v>
+      </c>
+      <c r="H55" s="2" t="str">
+        <f>_xlfn.XLOOKUP(E55,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
+        <v>PC269.png</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B56" t="s">
+        <v>33</v>
+      </c>
+      <c r="C56" t="s">
+        <v>28</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E56" t="s">
+        <v>44</v>
+      </c>
+      <c r="F56">
+        <v>2.29</v>
+      </c>
+      <c r="G56">
+        <v>2.09</v>
+      </c>
+      <c r="H56" s="2" t="str">
+        <f>_xlfn.XLOOKUP(E56,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
+        <v>PC269.png</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B57" t="s">
+        <v>4</v>
+      </c>
+      <c r="C57" t="s">
+        <v>29</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E57" t="s">
+        <v>34</v>
+      </c>
+      <c r="F57">
+        <v>5.29</v>
+      </c>
+      <c r="G57">
+        <v>4.99</v>
+      </c>
+      <c r="H57" s="2" t="str">
+        <f>_xlfn.XLOOKUP(E57,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
+        <v>GCAP1.png</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B58" t="s">
+        <v>30</v>
+      </c>
+      <c r="C58" t="s">
+        <v>29</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E58" t="s">
+        <v>35</v>
+      </c>
+      <c r="F58">
+        <v>6.99</v>
+      </c>
+      <c r="G58">
+        <v>6.69</v>
+      </c>
+      <c r="H58" s="2" t="str">
+        <f>_xlfn.XLOOKUP(E58,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
+        <v>GCAP1,5.png</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A59" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B59" t="s">
+        <v>31</v>
+      </c>
+      <c r="C59" t="s">
+        <v>29</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E59" t="s">
+        <v>35</v>
+      </c>
+      <c r="F59">
+        <v>6.99</v>
+      </c>
+      <c r="G59">
+        <v>6.69</v>
+      </c>
+      <c r="H59" s="2" t="str">
+        <f>_xlfn.XLOOKUP(E59,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
+        <v>GCAP1,5.png</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A60" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B60" t="s">
+        <v>32</v>
+      </c>
+      <c r="C60" t="s">
+        <v>29</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E60" t="s">
+        <v>35</v>
+      </c>
+      <c r="F60">
+        <v>6.99</v>
+      </c>
+      <c r="G60">
+        <v>6.69</v>
+      </c>
+      <c r="H60" s="2" t="str">
+        <f>_xlfn.XLOOKUP(E60,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
+        <v>GCAP1,5.png</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B61" t="s">
+        <v>33</v>
+      </c>
+      <c r="C61" t="s">
+        <v>29</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E61" t="s">
+        <v>35</v>
+      </c>
+      <c r="F61">
+        <v>6.99</v>
+      </c>
+      <c r="G61">
+        <v>6.69</v>
+      </c>
+      <c r="H61" s="2" t="str">
+        <f>_xlfn.XLOOKUP(E61,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
+        <v>GCAP1,5.png</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A62" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B62" t="s">
+        <v>4</v>
+      </c>
+      <c r="C62" t="s">
+        <v>29</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E62" t="s">
+        <v>36</v>
+      </c>
+      <c r="F62">
+        <v>7.99</v>
+      </c>
+      <c r="G62">
+        <v>7.49</v>
+      </c>
+      <c r="H62" s="2" t="str">
+        <f>_xlfn.XLOOKUP(E62,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
+        <v>PCP2.png</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A63" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B63" t="s">
+        <v>30</v>
+      </c>
+      <c r="C63" t="s">
+        <v>29</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E63" t="s">
+        <v>36</v>
+      </c>
+      <c r="F63">
+        <v>8.49</v>
+      </c>
+      <c r="G63">
+        <v>7.99</v>
+      </c>
+      <c r="H63" s="2" t="str">
+        <f>_xlfn.XLOOKUP(E63,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
+        <v>PCP2.png</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A64" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B64" t="s">
+        <v>31</v>
+      </c>
+      <c r="C64" t="s">
+        <v>29</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E64" t="s">
+        <v>36</v>
+      </c>
+      <c r="F64">
+        <v>7.69</v>
+      </c>
+      <c r="G64">
+        <v>7.19</v>
+      </c>
+      <c r="H64" s="2" t="str">
+        <f>_xlfn.XLOOKUP(E64,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
+        <v>PCP2.png</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A65" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B65" t="s">
+        <v>32</v>
+      </c>
+      <c r="C65" t="s">
+        <v>29</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E65" t="s">
+        <v>36</v>
+      </c>
+      <c r="F65">
+        <v>7.69</v>
+      </c>
+      <c r="G65">
+        <v>7.19</v>
+      </c>
+      <c r="H65" s="2" t="str">
+        <f>_xlfn.XLOOKUP(E65,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
+        <v>PCP2.png</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B66" t="s">
+        <v>33</v>
+      </c>
+      <c r="C66" t="s">
+        <v>29</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E66" t="s">
+        <v>36</v>
+      </c>
+      <c r="F66">
+        <v>8.49</v>
+      </c>
+      <c r="G66">
+        <v>7.99</v>
+      </c>
+      <c r="H66" s="2" t="str">
+        <f>_xlfn.XLOOKUP(E66,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
+        <v>PCP2.png</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A67" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B67" t="s">
+        <v>30</v>
+      </c>
+      <c r="C67" t="s">
+        <v>29</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E67" t="s">
+        <v>45</v>
+      </c>
+      <c r="F67">
+        <v>8.49</v>
+      </c>
+      <c r="G67">
+        <v>7.99</v>
+      </c>
+      <c r="H67" s="2" t="str">
+        <f>_xlfn.XLOOKUP(E67,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
+        <v>H2OHP1,5.png</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A68" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B68" t="s">
+        <v>31</v>
+      </c>
+      <c r="C68" t="s">
+        <v>29</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E68" t="s">
+        <v>45</v>
+      </c>
+      <c r="F68">
+        <v>7.99</v>
+      </c>
+      <c r="G68">
+        <v>7.49</v>
+      </c>
+      <c r="H68" s="2" t="str">
+        <f>_xlfn.XLOOKUP(E68,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
+        <v>H2OHP1,5.png</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A69" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B69" t="s">
+        <v>32</v>
+      </c>
+      <c r="C69" t="s">
+        <v>29</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E69" t="s">
+        <v>45</v>
+      </c>
+      <c r="F69">
+        <v>7.99</v>
+      </c>
+      <c r="G69">
+        <v>7.49</v>
+      </c>
+      <c r="H69" s="2" t="str">
+        <f>_xlfn.XLOOKUP(E69,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
+        <v>H2OHP1,5.png</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A70" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B70" t="s">
+        <v>33</v>
+      </c>
+      <c r="C70" t="s">
+        <v>29</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E70" t="s">
+        <v>45</v>
+      </c>
+      <c r="F70">
+        <v>8.49</v>
+      </c>
+      <c r="G70">
+        <v>7.99</v>
+      </c>
+      <c r="H70" s="2" t="str">
+        <f>_xlfn.XLOOKUP(E70,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
+        <v>H2OHP1,5.png</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A71" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B71" t="s">
+        <v>4</v>
+      </c>
+      <c r="C71" t="s">
+        <v>29</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E71" t="s">
+        <v>39</v>
+      </c>
+      <c r="F71">
+        <v>6.99</v>
+      </c>
+      <c r="G71">
+        <v>6.49</v>
+      </c>
+      <c r="H71" s="2" t="str">
+        <f>_xlfn.XLOOKUP(E71,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
+        <v>SUKP2.png</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A72" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B72" t="s">
+        <v>30</v>
+      </c>
+      <c r="C72" t="s">
+        <v>29</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E72" t="s">
+        <v>39</v>
+      </c>
+      <c r="F72">
+        <v>6.99</v>
+      </c>
+      <c r="G72">
+        <v>6.49</v>
+      </c>
+      <c r="H72" s="2" t="str">
+        <f>_xlfn.XLOOKUP(E72,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
+        <v>SUKP2.png</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A73" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B73" t="s">
+        <v>31</v>
+      </c>
+      <c r="C73" t="s">
+        <v>29</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E73" t="s">
+        <v>39</v>
+      </c>
+      <c r="F73">
+        <v>6.99</v>
+      </c>
+      <c r="G73">
+        <v>6.49</v>
+      </c>
+      <c r="H73" s="2" t="str">
+        <f>_xlfn.XLOOKUP(E73,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
+        <v>SUKP2.png</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A74" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B74" t="s">
+        <v>32</v>
+      </c>
+      <c r="C74" t="s">
+        <v>29</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E74" t="s">
+        <v>39</v>
+      </c>
+      <c r="F74">
+        <v>6.99</v>
+      </c>
+      <c r="G74">
+        <v>6.49</v>
+      </c>
+      <c r="H74" s="2" t="str">
+        <f>_xlfn.XLOOKUP(E74,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
+        <v>SUKP2.png</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A75" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B75" t="s">
+        <v>33</v>
+      </c>
+      <c r="C75" t="s">
+        <v>29</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E75" t="s">
+        <v>39</v>
+      </c>
+      <c r="F75">
+        <v>7.49</v>
+      </c>
+      <c r="G75">
+        <v>6.99</v>
+      </c>
+      <c r="H75" s="2" t="str">
+        <f>_xlfn.XLOOKUP(E75,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
+        <v>SUKP2.png</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D76" s="2"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:H75" xr:uid="{34B2C8DF-4561-40B2-8E7C-6CD69559B9AE}"/>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C08B3827-EDAF-4453-9F0C-3166EEE86952}">
   <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="B3" s="2">
         <v>2026</v>
@@ -857,7 +3254,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>4</v>
@@ -865,18 +3262,18 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/data/calendario_promocional.xlsx
+++ b/data/calendario_promocional.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://anheuserbuschinbev-my.sharepoint.com/personal/99823517_ab-inbev_com/Documents/001. Projetos/Streamlit Calendario/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="157" documentId="11_F25DC773A252ABDACC1048AAA9DA54025ADE5901" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AD2DA07D-C33E-41E1-BBE4-814A1D1B5B96}"/>
+  <xr:revisionPtr revIDLastSave="165" documentId="11_F25DC773A252ABDACC1048AAA9DA54025ADE5901" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{69E8D608-60B6-451C-B05A-810AF85AF3BE}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DeparaIMG" sheetId="5" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="63">
   <si>
     <t>Data</t>
   </si>
@@ -121,12 +121,6 @@
   </si>
   <si>
     <t>Sell out</t>
-  </si>
-  <si>
-    <t>1Q</t>
-  </si>
-  <si>
-    <t>2Q</t>
   </si>
   <si>
     <t>ATACADO</t>
@@ -596,18 +590,18 @@
         <v>7</v>
       </c>
       <c r="B1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C2" t="str">
         <f>B2&amp;".png"</f>
@@ -616,10 +610,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C3" t="str">
         <f t="shared" ref="C3:C13" si="0">B3&amp;".png"</f>
@@ -628,10 +622,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C4" t="str">
         <f t="shared" si="0"/>
@@ -640,10 +634,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B5" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C5" t="str">
         <f t="shared" si="0"/>
@@ -652,10 +646,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C6" t="str">
         <f t="shared" si="0"/>
@@ -664,10 +658,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B7" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C7" t="str">
         <f t="shared" si="0"/>
@@ -676,10 +670,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B8" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C8" t="str">
         <f t="shared" si="0"/>
@@ -688,10 +682,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B9" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C9" t="str">
         <f t="shared" si="0"/>
@@ -700,10 +694,10 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B10" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C10" t="str">
         <f t="shared" si="0"/>
@@ -712,10 +706,10 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B11" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C11" t="str">
         <f t="shared" si="0"/>
@@ -724,10 +718,10 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B12" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C12" t="str">
         <f t="shared" si="0"/>
@@ -736,10 +730,10 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B13" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C13" t="str">
         <f t="shared" si="0"/>
@@ -760,7 +754,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -1108,7 +1102,7 @@
         <v>24</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -1119,7 +1113,7 @@
         <v>24</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -1130,7 +1124,7 @@
         <v>24</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -1141,7 +1135,7 @@
         <v>24</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -1152,7 +1146,7 @@
         <v>25</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -1163,7 +1157,7 @@
         <v>25</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -1174,7 +1168,7 @@
         <v>25</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>
@@ -1224,13 +1218,13 @@
         <v>4</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>26</v>
+        <v>26</v>
+      </c>
+      <c r="D2" s="2">
+        <v>1</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F2" s="2">
         <v>4.99</v>
@@ -1248,16 +1242,16 @@
         <v>11</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>26</v>
+        <v>26</v>
+      </c>
+      <c r="D3" s="2">
+        <v>1</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F3" s="2">
         <v>6.49</v>
@@ -1275,16 +1269,16 @@
         <v>11</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>26</v>
+        <v>26</v>
+      </c>
+      <c r="D4" s="2">
+        <v>1</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F4" s="2">
         <v>6.49</v>
@@ -1302,16 +1296,16 @@
         <v>11</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>26</v>
+        <v>26</v>
+      </c>
+      <c r="D5" s="2">
+        <v>1</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F5" s="2">
         <v>6.49</v>
@@ -1329,16 +1323,16 @@
         <v>11</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" s="2">
+        <v>1</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>33</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>35</v>
       </c>
       <c r="F6" s="2">
         <v>6.49</v>
@@ -1359,13 +1353,13 @@
         <v>4</v>
       </c>
       <c r="C7" t="s">
-        <v>28</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>26</v>
+        <v>26</v>
+      </c>
+      <c r="D7" s="2">
+        <v>1</v>
       </c>
       <c r="E7" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F7">
         <v>7.79</v>
@@ -1383,16 +1377,16 @@
         <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C8" t="s">
-        <v>28</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>26</v>
+        <v>26</v>
+      </c>
+      <c r="D8" s="2">
+        <v>1</v>
       </c>
       <c r="E8" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F8">
         <v>8.49</v>
@@ -1410,16 +1404,16 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>28</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>26</v>
+        <v>26</v>
+      </c>
+      <c r="D9" s="2">
+        <v>1</v>
       </c>
       <c r="E9" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F9">
         <v>7.49</v>
@@ -1437,16 +1431,16 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C10" t="s">
-        <v>28</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>26</v>
+        <v>26</v>
+      </c>
+      <c r="D10" s="2">
+        <v>1</v>
       </c>
       <c r="E10" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F10">
         <v>7.49</v>
@@ -1464,16 +1458,16 @@
         <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C11" t="s">
-        <v>28</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>26</v>
+        <v>26</v>
+      </c>
+      <c r="D11" s="2">
+        <v>1</v>
       </c>
       <c r="E11" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F11">
         <v>8.49</v>
@@ -1494,13 +1488,13 @@
         <v>4</v>
       </c>
       <c r="C12" t="s">
-        <v>28</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>26</v>
+        <v>26</v>
+      </c>
+      <c r="D12" s="2">
+        <v>1</v>
       </c>
       <c r="E12" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F12">
         <v>5.49</v>
@@ -1518,16 +1512,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C13" t="s">
-        <v>28</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>26</v>
+        <v>26</v>
+      </c>
+      <c r="D13" s="2">
+        <v>1</v>
       </c>
       <c r="E13" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F13">
         <v>5.29</v>
@@ -1545,16 +1539,16 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C14" t="s">
-        <v>28</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>26</v>
+        <v>26</v>
+      </c>
+      <c r="D14" s="2">
+        <v>1</v>
       </c>
       <c r="E14" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F14">
         <v>5.29</v>
@@ -1572,16 +1566,16 @@
         <v>11</v>
       </c>
       <c r="B15" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C15" t="s">
-        <v>28</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>26</v>
+        <v>26</v>
+      </c>
+      <c r="D15" s="2">
+        <v>1</v>
       </c>
       <c r="E15" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F15">
         <v>5.29</v>
@@ -1599,16 +1593,16 @@
         <v>11</v>
       </c>
       <c r="B16" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C16" t="s">
-        <v>28</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>26</v>
+        <v>26</v>
+      </c>
+      <c r="D16" s="2">
+        <v>1</v>
       </c>
       <c r="E16" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F16">
         <v>5.29</v>
@@ -1629,13 +1623,13 @@
         <v>4</v>
       </c>
       <c r="C17" t="s">
-        <v>28</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>26</v>
+        <v>26</v>
+      </c>
+      <c r="D17" s="2">
+        <v>1</v>
       </c>
       <c r="E17" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F17">
         <v>6.79</v>
@@ -1653,16 +1647,16 @@
         <v>11</v>
       </c>
       <c r="B18" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C18" t="s">
-        <v>28</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>26</v>
+        <v>26</v>
+      </c>
+      <c r="D18" s="2">
+        <v>1</v>
       </c>
       <c r="E18" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F18">
         <v>6.79</v>
@@ -1680,16 +1674,16 @@
         <v>11</v>
       </c>
       <c r="B19" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C19" t="s">
-        <v>28</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>26</v>
+        <v>26</v>
+      </c>
+      <c r="D19" s="2">
+        <v>1</v>
       </c>
       <c r="E19" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F19">
         <v>6.79</v>
@@ -1707,16 +1701,16 @@
         <v>11</v>
       </c>
       <c r="B20" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C20" t="s">
-        <v>28</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>26</v>
+        <v>26</v>
+      </c>
+      <c r="D20" s="2">
+        <v>1</v>
       </c>
       <c r="E20" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F20">
         <v>6.79</v>
@@ -1734,16 +1728,16 @@
         <v>11</v>
       </c>
       <c r="B21" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C21" t="s">
-        <v>28</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>26</v>
+        <v>26</v>
+      </c>
+      <c r="D21" s="2">
+        <v>1</v>
       </c>
       <c r="E21" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F21">
         <v>7.29</v>
@@ -1764,13 +1758,13 @@
         <v>4</v>
       </c>
       <c r="C22" t="s">
-        <v>29</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="D22" s="2">
+        <v>1</v>
       </c>
       <c r="E22" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F22">
         <v>8.99</v>
@@ -1788,16 +1782,16 @@
         <v>11</v>
       </c>
       <c r="B23" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C23" t="s">
-        <v>29</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="D23" s="2">
+        <v>1</v>
       </c>
       <c r="E23" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F23">
         <v>8.99</v>
@@ -1815,16 +1809,16 @@
         <v>11</v>
       </c>
       <c r="B24" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C24" t="s">
-        <v>29</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="D24" s="2">
+        <v>1</v>
       </c>
       <c r="E24" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F24">
         <v>8.2899999999999991</v>
@@ -1842,16 +1836,16 @@
         <v>11</v>
       </c>
       <c r="B25" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C25" t="s">
-        <v>29</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="D25" s="2">
+        <v>1</v>
       </c>
       <c r="E25" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F25">
         <v>8.2899999999999991</v>
@@ -1869,16 +1863,16 @@
         <v>11</v>
       </c>
       <c r="B26" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C26" t="s">
-        <v>29</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="D26" s="2">
+        <v>1</v>
       </c>
       <c r="E26" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F26">
         <v>9.49</v>
@@ -1899,13 +1893,13 @@
         <v>4</v>
       </c>
       <c r="C27" t="s">
-        <v>29</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="D27" s="2">
+        <v>1</v>
       </c>
       <c r="E27" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F27">
         <v>3.49</v>
@@ -1923,16 +1917,16 @@
         <v>11</v>
       </c>
       <c r="B28" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C28" t="s">
-        <v>29</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="D28" s="2">
+        <v>1</v>
       </c>
       <c r="E28" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F28">
         <v>3.49</v>
@@ -1950,16 +1944,16 @@
         <v>11</v>
       </c>
       <c r="B29" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C29" t="s">
-        <v>29</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="D29" s="2">
+        <v>1</v>
       </c>
       <c r="E29" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F29">
         <v>3.49</v>
@@ -1977,16 +1971,16 @@
         <v>11</v>
       </c>
       <c r="B30" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C30" t="s">
-        <v>29</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="D30" s="2">
+        <v>1</v>
       </c>
       <c r="E30" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F30">
         <v>3.49</v>
@@ -2004,16 +1998,16 @@
         <v>11</v>
       </c>
       <c r="B31" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C31" t="s">
-        <v>29</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="D31" s="2">
+        <v>1</v>
       </c>
       <c r="E31" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F31">
         <v>3.49</v>
@@ -2034,13 +2028,13 @@
         <v>4</v>
       </c>
       <c r="C32" t="s">
-        <v>29</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="D32" s="2">
+        <v>1</v>
       </c>
       <c r="E32" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F32">
         <v>5.69</v>
@@ -2058,16 +2052,16 @@
         <v>11</v>
       </c>
       <c r="B33" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C33" t="s">
-        <v>29</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="D33" s="2">
+        <v>1</v>
       </c>
       <c r="E33" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F33">
         <v>5.49</v>
@@ -2085,16 +2079,16 @@
         <v>11</v>
       </c>
       <c r="B34" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C34" t="s">
-        <v>29</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="D34" s="2">
+        <v>1</v>
       </c>
       <c r="E34" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F34">
         <v>5.49</v>
@@ -2112,16 +2106,16 @@
         <v>11</v>
       </c>
       <c r="B35" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C35" t="s">
-        <v>29</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="D35" s="2">
+        <v>1</v>
       </c>
       <c r="E35" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F35">
         <v>5.49</v>
@@ -2139,16 +2133,16 @@
         <v>11</v>
       </c>
       <c r="B36" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C36" t="s">
-        <v>29</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="D36" s="2">
+        <v>1</v>
       </c>
       <c r="E36" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F36">
         <v>5.49</v>
@@ -2169,13 +2163,13 @@
         <v>4</v>
       </c>
       <c r="C37" t="s">
-        <v>29</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="D37" s="2">
+        <v>1</v>
       </c>
       <c r="E37" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F37">
         <v>3.39</v>
@@ -2193,16 +2187,16 @@
         <v>11</v>
       </c>
       <c r="B38" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C38" t="s">
-        <v>29</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="D38" s="2">
+        <v>1</v>
       </c>
       <c r="E38" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F38">
         <v>3.39</v>
@@ -2220,16 +2214,16 @@
         <v>11</v>
       </c>
       <c r="B39" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C39" t="s">
-        <v>29</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="D39" s="2">
+        <v>1</v>
       </c>
       <c r="E39" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F39">
         <v>3.39</v>
@@ -2247,16 +2241,16 @@
         <v>11</v>
       </c>
       <c r="B40" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C40" t="s">
-        <v>29</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="D40" s="2">
+        <v>1</v>
       </c>
       <c r="E40" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F40">
         <v>3.39</v>
@@ -2274,16 +2268,16 @@
         <v>11</v>
       </c>
       <c r="B41" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C41" t="s">
-        <v>29</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="D41" s="2">
+        <v>1</v>
       </c>
       <c r="E41" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F41">
         <v>3.39</v>
@@ -2304,13 +2298,13 @@
         <v>4</v>
       </c>
       <c r="C42" t="s">
-        <v>28</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
+      </c>
+      <c r="D42" s="2">
+        <v>2</v>
       </c>
       <c r="E42" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F42">
         <v>8.7899999999999991</v>
@@ -2328,16 +2322,16 @@
         <v>11</v>
       </c>
       <c r="B43" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C43" t="s">
-        <v>28</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
+      </c>
+      <c r="D43" s="2">
+        <v>2</v>
       </c>
       <c r="E43" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F43">
         <v>8.7899999999999991</v>
@@ -2355,16 +2349,16 @@
         <v>11</v>
       </c>
       <c r="B44" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C44" t="s">
-        <v>28</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
+      </c>
+      <c r="D44" s="2">
+        <v>2</v>
       </c>
       <c r="E44" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F44">
         <v>7.99</v>
@@ -2382,16 +2376,16 @@
         <v>11</v>
       </c>
       <c r="B45" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C45" t="s">
-        <v>28</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
+      </c>
+      <c r="D45" s="2">
+        <v>2</v>
       </c>
       <c r="E45" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F45">
         <v>7.99</v>
@@ -2409,16 +2403,16 @@
         <v>11</v>
       </c>
       <c r="B46" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C46" t="s">
-        <v>28</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
+      </c>
+      <c r="D46" s="2">
+        <v>2</v>
       </c>
       <c r="E46" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F46">
         <v>9.2899999999999991</v>
@@ -2439,13 +2433,13 @@
         <v>4</v>
       </c>
       <c r="C47" t="s">
-        <v>28</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
+      </c>
+      <c r="D47" s="2">
+        <v>2</v>
       </c>
       <c r="E47" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F47">
         <v>2.39</v>
@@ -2463,16 +2457,16 @@
         <v>11</v>
       </c>
       <c r="B48" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C48" t="s">
-        <v>28</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
+      </c>
+      <c r="D48" s="2">
+        <v>2</v>
       </c>
       <c r="E48" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F48">
         <v>2.39</v>
@@ -2490,16 +2484,16 @@
         <v>11</v>
       </c>
       <c r="B49" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C49" t="s">
-        <v>28</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
+      </c>
+      <c r="D49" s="2">
+        <v>2</v>
       </c>
       <c r="E49" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F49">
         <v>2.39</v>
@@ -2517,16 +2511,16 @@
         <v>11</v>
       </c>
       <c r="B50" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C50" t="s">
-        <v>28</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
+      </c>
+      <c r="D50" s="2">
+        <v>2</v>
       </c>
       <c r="E50" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F50">
         <v>2.39</v>
@@ -2544,16 +2538,16 @@
         <v>11</v>
       </c>
       <c r="B51" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C51" t="s">
-        <v>28</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
+      </c>
+      <c r="D51" s="2">
+        <v>2</v>
       </c>
       <c r="E51" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F51">
         <v>2.39</v>
@@ -2574,13 +2568,13 @@
         <v>4</v>
       </c>
       <c r="C52" t="s">
-        <v>28</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
+      </c>
+      <c r="D52" s="2">
+        <v>2</v>
       </c>
       <c r="E52" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F52">
         <v>2.29</v>
@@ -2598,16 +2592,16 @@
         <v>11</v>
       </c>
       <c r="B53" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C53" t="s">
-        <v>28</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
+      </c>
+      <c r="D53" s="2">
+        <v>2</v>
       </c>
       <c r="E53" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F53">
         <v>2.29</v>
@@ -2625,16 +2619,16 @@
         <v>11</v>
       </c>
       <c r="B54" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C54" t="s">
-        <v>28</v>
-      </c>
-      <c r="D54" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
+      </c>
+      <c r="D54" s="2">
+        <v>2</v>
       </c>
       <c r="E54" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F54">
         <v>2.29</v>
@@ -2652,16 +2646,16 @@
         <v>11</v>
       </c>
       <c r="B55" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C55" t="s">
-        <v>28</v>
-      </c>
-      <c r="D55" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
+      </c>
+      <c r="D55" s="2">
+        <v>2</v>
       </c>
       <c r="E55" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F55">
         <v>2.29</v>
@@ -2679,16 +2673,16 @@
         <v>11</v>
       </c>
       <c r="B56" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C56" t="s">
-        <v>28</v>
-      </c>
-      <c r="D56" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
+      </c>
+      <c r="D56" s="2">
+        <v>2</v>
       </c>
       <c r="E56" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F56">
         <v>2.29</v>
@@ -2709,13 +2703,13 @@
         <v>4</v>
       </c>
       <c r="C57" t="s">
-        <v>29</v>
-      </c>
-      <c r="D57" s="2" t="s">
-        <v>27</v>
+        <v>27</v>
+      </c>
+      <c r="D57" s="2">
+        <v>2</v>
       </c>
       <c r="E57" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F57">
         <v>5.29</v>
@@ -2733,16 +2727,16 @@
         <v>11</v>
       </c>
       <c r="B58" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C58" t="s">
-        <v>29</v>
-      </c>
-      <c r="D58" s="2" t="s">
-        <v>27</v>
+        <v>27</v>
+      </c>
+      <c r="D58" s="2">
+        <v>2</v>
       </c>
       <c r="E58" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F58">
         <v>6.99</v>
@@ -2760,16 +2754,16 @@
         <v>11</v>
       </c>
       <c r="B59" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C59" t="s">
-        <v>29</v>
-      </c>
-      <c r="D59" s="2" t="s">
-        <v>27</v>
+        <v>27</v>
+      </c>
+      <c r="D59" s="2">
+        <v>2</v>
       </c>
       <c r="E59" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F59">
         <v>6.99</v>
@@ -2787,16 +2781,16 @@
         <v>11</v>
       </c>
       <c r="B60" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C60" t="s">
-        <v>29</v>
-      </c>
-      <c r="D60" s="2" t="s">
-        <v>27</v>
+        <v>27</v>
+      </c>
+      <c r="D60" s="2">
+        <v>2</v>
       </c>
       <c r="E60" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F60">
         <v>6.99</v>
@@ -2814,16 +2808,16 @@
         <v>11</v>
       </c>
       <c r="B61" t="s">
+        <v>31</v>
+      </c>
+      <c r="C61" t="s">
+        <v>27</v>
+      </c>
+      <c r="D61" s="2">
+        <v>2</v>
+      </c>
+      <c r="E61" t="s">
         <v>33</v>
-      </c>
-      <c r="C61" t="s">
-        <v>29</v>
-      </c>
-      <c r="D61" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E61" t="s">
-        <v>35</v>
       </c>
       <c r="F61">
         <v>6.99</v>
@@ -2844,13 +2838,13 @@
         <v>4</v>
       </c>
       <c r="C62" t="s">
-        <v>29</v>
-      </c>
-      <c r="D62" s="2" t="s">
-        <v>27</v>
+        <v>27</v>
+      </c>
+      <c r="D62" s="2">
+        <v>2</v>
       </c>
       <c r="E62" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F62">
         <v>7.99</v>
@@ -2868,16 +2862,16 @@
         <v>11</v>
       </c>
       <c r="B63" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C63" t="s">
-        <v>29</v>
-      </c>
-      <c r="D63" s="2" t="s">
-        <v>27</v>
+        <v>27</v>
+      </c>
+      <c r="D63" s="2">
+        <v>2</v>
       </c>
       <c r="E63" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F63">
         <v>8.49</v>
@@ -2895,16 +2889,16 @@
         <v>11</v>
       </c>
       <c r="B64" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C64" t="s">
-        <v>29</v>
-      </c>
-      <c r="D64" s="2" t="s">
-        <v>27</v>
+        <v>27</v>
+      </c>
+      <c r="D64" s="2">
+        <v>2</v>
       </c>
       <c r="E64" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F64">
         <v>7.69</v>
@@ -2922,16 +2916,16 @@
         <v>11</v>
       </c>
       <c r="B65" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C65" t="s">
-        <v>29</v>
-      </c>
-      <c r="D65" s="2" t="s">
-        <v>27</v>
+        <v>27</v>
+      </c>
+      <c r="D65" s="2">
+        <v>2</v>
       </c>
       <c r="E65" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F65">
         <v>7.69</v>
@@ -2949,16 +2943,16 @@
         <v>11</v>
       </c>
       <c r="B66" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C66" t="s">
-        <v>29</v>
-      </c>
-      <c r="D66" s="2" t="s">
-        <v>27</v>
+        <v>27</v>
+      </c>
+      <c r="D66" s="2">
+        <v>2</v>
       </c>
       <c r="E66" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F66">
         <v>8.49</v>
@@ -2976,16 +2970,16 @@
         <v>11</v>
       </c>
       <c r="B67" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C67" t="s">
-        <v>29</v>
-      </c>
-      <c r="D67" s="2" t="s">
-        <v>27</v>
+        <v>27</v>
+      </c>
+      <c r="D67" s="2">
+        <v>2</v>
       </c>
       <c r="E67" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F67">
         <v>8.49</v>
@@ -3003,16 +2997,16 @@
         <v>11</v>
       </c>
       <c r="B68" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C68" t="s">
-        <v>29</v>
-      </c>
-      <c r="D68" s="2" t="s">
-        <v>27</v>
+        <v>27</v>
+      </c>
+      <c r="D68" s="2">
+        <v>2</v>
       </c>
       <c r="E68" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F68">
         <v>7.99</v>
@@ -3030,16 +3024,16 @@
         <v>11</v>
       </c>
       <c r="B69" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C69" t="s">
-        <v>29</v>
-      </c>
-      <c r="D69" s="2" t="s">
-        <v>27</v>
+        <v>27</v>
+      </c>
+      <c r="D69" s="2">
+        <v>2</v>
       </c>
       <c r="E69" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F69">
         <v>7.99</v>
@@ -3057,16 +3051,16 @@
         <v>11</v>
       </c>
       <c r="B70" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C70" t="s">
-        <v>29</v>
-      </c>
-      <c r="D70" s="2" t="s">
-        <v>27</v>
+        <v>27</v>
+      </c>
+      <c r="D70" s="2">
+        <v>2</v>
       </c>
       <c r="E70" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F70">
         <v>8.49</v>
@@ -3087,13 +3081,13 @@
         <v>4</v>
       </c>
       <c r="C71" t="s">
-        <v>29</v>
-      </c>
-      <c r="D71" s="2" t="s">
-        <v>27</v>
+        <v>27</v>
+      </c>
+      <c r="D71" s="2">
+        <v>2</v>
       </c>
       <c r="E71" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F71">
         <v>6.99</v>
@@ -3111,16 +3105,16 @@
         <v>11</v>
       </c>
       <c r="B72" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C72" t="s">
-        <v>29</v>
-      </c>
-      <c r="D72" s="2" t="s">
-        <v>27</v>
+        <v>27</v>
+      </c>
+      <c r="D72" s="2">
+        <v>2</v>
       </c>
       <c r="E72" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F72">
         <v>6.99</v>
@@ -3138,16 +3132,16 @@
         <v>11</v>
       </c>
       <c r="B73" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C73" t="s">
-        <v>29</v>
-      </c>
-      <c r="D73" s="2" t="s">
-        <v>27</v>
+        <v>27</v>
+      </c>
+      <c r="D73" s="2">
+        <v>2</v>
       </c>
       <c r="E73" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F73">
         <v>6.99</v>
@@ -3165,16 +3159,16 @@
         <v>11</v>
       </c>
       <c r="B74" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C74" t="s">
-        <v>29</v>
-      </c>
-      <c r="D74" s="2" t="s">
-        <v>27</v>
+        <v>27</v>
+      </c>
+      <c r="D74" s="2">
+        <v>2</v>
       </c>
       <c r="E74" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F74">
         <v>6.99</v>
@@ -3192,16 +3186,16 @@
         <v>11</v>
       </c>
       <c r="B75" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C75" t="s">
-        <v>29</v>
-      </c>
-      <c r="D75" s="2" t="s">
-        <v>27</v>
+        <v>27</v>
+      </c>
+      <c r="D75" s="2">
+        <v>2</v>
       </c>
       <c r="E75" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F75">
         <v>7.49</v>

--- a/data/calendario_promocional.xlsx
+++ b/data/calendario_promocional.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://anheuserbuschinbev-my.sharepoint.com/personal/99823517_ab-inbev_com/Documents/001. Projetos/Streamlit Calendario/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="165" documentId="11_F25DC773A252ABDACC1048AAA9DA54025ADE5901" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{69E8D608-60B6-451C-B05A-810AF85AF3BE}"/>
+  <xr:revisionPtr revIDLastSave="178" documentId="11_F25DC773A252ABDACC1048AAA9DA54025ADE5901" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{757B16F3-0C7C-4F1C-8843-35D053D6DCF3}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DeparaIMG" sheetId="5" r:id="rId1"/>
@@ -20,7 +20,7 @@
     <sheet name="CONFIG" sheetId="4" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">PRODUTOS!$A$1:$H$75</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">PRODUTOS!$A$1:$I$75</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="485" uniqueCount="64">
   <si>
     <t>Data</t>
   </si>
@@ -232,6 +232,9 @@
   </si>
   <si>
     <t>Apuração Varejo: 100% no períiodo, com check de TTC</t>
+  </si>
+  <si>
+    <t>NAB</t>
   </si>
 </sst>
 </file>
@@ -1077,97 +1080,121 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D40F4A5-E774-499A-A01D-1C21EEE25028}">
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="47.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="47.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="2" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="D5" s="2" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B7" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="2" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="D8" s="2" t="s">
         <v>62</v>
       </c>
     </row>
@@ -1178,2041 +1205,2266 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34B2C8DF-4561-40B2-8E7C-6CD69559B9AE}">
-  <dimension ref="A1:H76"/>
+  <dimension ref="A1:I76"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="8" max="8" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="D2" s="2">
-        <v>1</v>
-      </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="2">
+        <v>1</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="F2" s="2">
+      <c r="G2" s="2">
         <v>4.99</v>
       </c>
-      <c r="G2" s="2">
+      <c r="H2" s="2">
         <v>4.6900000000000004</v>
       </c>
-      <c r="H2" s="2" t="str">
-        <f>_xlfn.XLOOKUP(E2,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
+      <c r="I2" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F2,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
         <v>GCAP1.png</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="D3" s="2">
-        <v>1</v>
-      </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="2">
+        <v>1</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="F3" s="2">
+      <c r="G3" s="2">
         <v>6.49</v>
       </c>
-      <c r="G3" s="2">
+      <c r="H3" s="2">
         <v>6.19</v>
       </c>
-      <c r="H3" s="2" t="str">
-        <f>_xlfn.XLOOKUP(E3,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
+      <c r="I3" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F3,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
         <v>GCAP1,5.png</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="D4" s="2">
-        <v>1</v>
-      </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="2">
+        <v>1</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="F4" s="2">
+      <c r="G4" s="2">
         <v>6.49</v>
       </c>
-      <c r="G4" s="2">
+      <c r="H4" s="2">
         <v>6.19</v>
       </c>
-      <c r="H4" s="2" t="str">
-        <f>_xlfn.XLOOKUP(E4,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
+      <c r="I4" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F4,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
         <v>GCAP1,5.png</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="D5" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="D5" s="2">
-        <v>1</v>
-      </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="2">
+        <v>1</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="F5" s="2">
+      <c r="G5" s="2">
         <v>6.49</v>
       </c>
-      <c r="G5" s="2">
+      <c r="H5" s="2">
         <v>6.19</v>
       </c>
-      <c r="H5" s="2" t="str">
-        <f>_xlfn.XLOOKUP(E5,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
+      <c r="I5" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F5,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
         <v>GCAP1,5.png</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="D6" s="2">
-        <v>1</v>
-      </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" s="2">
+        <v>1</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="F6" s="2">
+      <c r="G6" s="2">
         <v>6.49</v>
       </c>
-      <c r="G6" s="2">
+      <c r="H6" s="2">
         <v>6.19</v>
       </c>
-      <c r="H6" s="2" t="str">
-        <f>_xlfn.XLOOKUP(E6,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
+      <c r="I6" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F6,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
         <v>GCAP1,5.png</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C7" t="s">
         <v>4</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
         <v>26</v>
       </c>
-      <c r="D7" s="2">
-        <v>1</v>
-      </c>
-      <c r="E7" t="s">
+      <c r="E7" s="2">
+        <v>1</v>
+      </c>
+      <c r="F7" t="s">
         <v>34</v>
       </c>
-      <c r="F7">
+      <c r="G7">
         <v>7.79</v>
       </c>
-      <c r="G7">
+      <c r="H7">
         <v>7.29</v>
       </c>
-      <c r="H7" s="2" t="str">
-        <f>_xlfn.XLOOKUP(E7,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
+      <c r="I7" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F7,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
         <v>PCP2.png</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C8" t="s">
         <v>28</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>26</v>
       </c>
-      <c r="D8" s="2">
-        <v>1</v>
-      </c>
-      <c r="E8" t="s">
+      <c r="E8" s="2">
+        <v>1</v>
+      </c>
+      <c r="F8" t="s">
         <v>34</v>
       </c>
-      <c r="F8">
+      <c r="G8">
         <v>8.49</v>
       </c>
-      <c r="G8">
+      <c r="H8">
         <v>7.99</v>
       </c>
-      <c r="H8" s="2" t="str">
-        <f>_xlfn.XLOOKUP(E8,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
+      <c r="I8" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F8,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
         <v>PCP2.png</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C9" t="s">
         <v>29</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
         <v>26</v>
       </c>
-      <c r="D9" s="2">
-        <v>1</v>
-      </c>
-      <c r="E9" t="s">
+      <c r="E9" s="2">
+        <v>1</v>
+      </c>
+      <c r="F9" t="s">
         <v>34</v>
       </c>
-      <c r="F9">
+      <c r="G9">
         <v>7.49</v>
       </c>
-      <c r="G9">
+      <c r="H9">
         <v>6.99</v>
       </c>
-      <c r="H9" s="2" t="str">
-        <f>_xlfn.XLOOKUP(E9,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
+      <c r="I9" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F9,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
         <v>PCP2.png</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C10" t="s">
         <v>30</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
         <v>26</v>
       </c>
-      <c r="D10" s="2">
-        <v>1</v>
-      </c>
-      <c r="E10" t="s">
+      <c r="E10" s="2">
+        <v>1</v>
+      </c>
+      <c r="F10" t="s">
         <v>34</v>
       </c>
-      <c r="F10">
+      <c r="G10">
         <v>7.49</v>
       </c>
-      <c r="G10">
+      <c r="H10">
         <v>6.99</v>
       </c>
-      <c r="H10" s="2" t="str">
-        <f>_xlfn.XLOOKUP(E10,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
+      <c r="I10" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F10,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
         <v>PCP2.png</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C11" t="s">
         <v>31</v>
       </c>
-      <c r="C11" t="s">
+      <c r="D11" t="s">
         <v>26</v>
       </c>
-      <c r="D11" s="2">
-        <v>1</v>
-      </c>
-      <c r="E11" t="s">
+      <c r="E11" s="2">
+        <v>1</v>
+      </c>
+      <c r="F11" t="s">
         <v>34</v>
       </c>
-      <c r="F11">
+      <c r="G11">
         <v>8.49</v>
       </c>
-      <c r="G11">
+      <c r="H11">
         <v>7.99</v>
       </c>
-      <c r="H11" s="2" t="str">
-        <f>_xlfn.XLOOKUP(E11,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
+      <c r="I11" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F11,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
         <v>PCP2.png</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C12" t="s">
         <v>4</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
         <v>26</v>
       </c>
-      <c r="D12" s="2">
-        <v>1</v>
-      </c>
-      <c r="E12" t="s">
+      <c r="E12" s="2">
+        <v>1</v>
+      </c>
+      <c r="F12" t="s">
         <v>35</v>
       </c>
-      <c r="F12">
+      <c r="G12">
         <v>5.49</v>
       </c>
-      <c r="G12">
+      <c r="H12">
         <v>5.19</v>
       </c>
-      <c r="H12" s="2" t="str">
-        <f>_xlfn.XLOOKUP(E12,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
+      <c r="I12" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F12,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
         <v>BAREP2.png</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C13" t="s">
         <v>28</v>
       </c>
-      <c r="C13" t="s">
+      <c r="D13" t="s">
         <v>26</v>
       </c>
-      <c r="D13" s="2">
-        <v>1</v>
-      </c>
-      <c r="E13" t="s">
+      <c r="E13" s="2">
+        <v>1</v>
+      </c>
+      <c r="F13" t="s">
         <v>36</v>
       </c>
-      <c r="F13">
+      <c r="G13">
         <v>5.29</v>
       </c>
-      <c r="G13">
+      <c r="H13">
         <v>4.99</v>
       </c>
-      <c r="H13" s="2" t="str">
-        <f>_xlfn.XLOOKUP(E13,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
+      <c r="I13" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F13,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
         <v>H2OHP500.png</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C14" t="s">
         <v>29</v>
       </c>
-      <c r="C14" t="s">
+      <c r="D14" t="s">
         <v>26</v>
       </c>
-      <c r="D14" s="2">
-        <v>1</v>
-      </c>
-      <c r="E14" t="s">
+      <c r="E14" s="2">
+        <v>1</v>
+      </c>
+      <c r="F14" t="s">
         <v>36</v>
       </c>
-      <c r="F14">
+      <c r="G14">
         <v>5.29</v>
       </c>
-      <c r="G14">
+      <c r="H14">
         <v>4.99</v>
       </c>
-      <c r="H14" s="2" t="str">
-        <f>_xlfn.XLOOKUP(E14,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
+      <c r="I14" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F14,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
         <v>H2OHP500.png</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C15" t="s">
         <v>30</v>
       </c>
-      <c r="C15" t="s">
+      <c r="D15" t="s">
         <v>26</v>
       </c>
-      <c r="D15" s="2">
-        <v>1</v>
-      </c>
-      <c r="E15" t="s">
+      <c r="E15" s="2">
+        <v>1</v>
+      </c>
+      <c r="F15" t="s">
         <v>36</v>
       </c>
-      <c r="F15">
+      <c r="G15">
         <v>5.29</v>
       </c>
-      <c r="G15">
+      <c r="H15">
         <v>4.99</v>
       </c>
-      <c r="H15" s="2" t="str">
-        <f>_xlfn.XLOOKUP(E15,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
+      <c r="I15" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F15,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
         <v>H2OHP500.png</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C16" t="s">
         <v>31</v>
       </c>
-      <c r="C16" t="s">
+      <c r="D16" t="s">
         <v>26</v>
       </c>
-      <c r="D16" s="2">
-        <v>1</v>
-      </c>
-      <c r="E16" t="s">
+      <c r="E16" s="2">
+        <v>1</v>
+      </c>
+      <c r="F16" t="s">
         <v>36</v>
       </c>
-      <c r="F16">
+      <c r="G16">
         <v>5.29</v>
       </c>
-      <c r="G16">
+      <c r="H16">
         <v>4.99</v>
       </c>
-      <c r="H16" s="2" t="str">
-        <f>_xlfn.XLOOKUP(E16,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
+      <c r="I16" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F16,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
         <v>H2OHP500.png</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C17" t="s">
         <v>4</v>
       </c>
-      <c r="C17" t="s">
+      <c r="D17" t="s">
         <v>26</v>
       </c>
-      <c r="D17" s="2">
-        <v>1</v>
-      </c>
-      <c r="E17" t="s">
+      <c r="E17" s="2">
+        <v>1</v>
+      </c>
+      <c r="F17" t="s">
         <v>37</v>
       </c>
-      <c r="F17">
+      <c r="G17">
         <v>6.79</v>
       </c>
-      <c r="G17">
+      <c r="H17">
         <v>6.29</v>
       </c>
-      <c r="H17" s="2" t="str">
-        <f>_xlfn.XLOOKUP(E17,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
+      <c r="I17" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F17,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
         <v>SUKP2.png</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C18" t="s">
         <v>28</v>
       </c>
-      <c r="C18" t="s">
+      <c r="D18" t="s">
         <v>26</v>
       </c>
-      <c r="D18" s="2">
-        <v>1</v>
-      </c>
-      <c r="E18" t="s">
+      <c r="E18" s="2">
+        <v>1</v>
+      </c>
+      <c r="F18" t="s">
         <v>37</v>
       </c>
-      <c r="F18">
+      <c r="G18">
         <v>6.79</v>
       </c>
-      <c r="G18">
+      <c r="H18">
         <v>6.29</v>
       </c>
-      <c r="H18" s="2" t="str">
-        <f>_xlfn.XLOOKUP(E18,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
+      <c r="I18" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F18,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
         <v>SUKP2.png</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C19" t="s">
         <v>29</v>
       </c>
-      <c r="C19" t="s">
+      <c r="D19" t="s">
         <v>26</v>
       </c>
-      <c r="D19" s="2">
-        <v>1</v>
-      </c>
-      <c r="E19" t="s">
+      <c r="E19" s="2">
+        <v>1</v>
+      </c>
+      <c r="F19" t="s">
         <v>37</v>
       </c>
-      <c r="F19">
+      <c r="G19">
         <v>6.79</v>
       </c>
-      <c r="G19">
+      <c r="H19">
         <v>6.29</v>
       </c>
-      <c r="H19" s="2" t="str">
-        <f>_xlfn.XLOOKUP(E19,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
+      <c r="I19" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F19,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
         <v>SUKP2.png</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C20" t="s">
         <v>30</v>
       </c>
-      <c r="C20" t="s">
+      <c r="D20" t="s">
         <v>26</v>
       </c>
-      <c r="D20" s="2">
-        <v>1</v>
-      </c>
-      <c r="E20" t="s">
+      <c r="E20" s="2">
+        <v>1</v>
+      </c>
+      <c r="F20" t="s">
         <v>37</v>
       </c>
-      <c r="F20">
+      <c r="G20">
         <v>6.79</v>
       </c>
-      <c r="G20">
+      <c r="H20">
         <v>6.29</v>
       </c>
-      <c r="H20" s="2" t="str">
-        <f>_xlfn.XLOOKUP(E20,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
+      <c r="I20" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F20,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
         <v>SUKP2.png</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C21" t="s">
         <v>31</v>
       </c>
-      <c r="C21" t="s">
+      <c r="D21" t="s">
         <v>26</v>
       </c>
-      <c r="D21" s="2">
-        <v>1</v>
-      </c>
-      <c r="E21" t="s">
+      <c r="E21" s="2">
+        <v>1</v>
+      </c>
+      <c r="F21" t="s">
         <v>37</v>
       </c>
-      <c r="F21">
+      <c r="G21">
         <v>7.29</v>
       </c>
-      <c r="G21">
+      <c r="H21">
         <v>6.79</v>
       </c>
-      <c r="H21" s="2" t="str">
-        <f>_xlfn.XLOOKUP(E21,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
+      <c r="I21" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F21,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
         <v>SUKP2.png</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C22" t="s">
         <v>4</v>
       </c>
-      <c r="C22" t="s">
-        <v>27</v>
-      </c>
-      <c r="D22" s="2">
-        <v>1</v>
-      </c>
-      <c r="E22" t="s">
+      <c r="D22" t="s">
+        <v>27</v>
+      </c>
+      <c r="E22" s="2">
+        <v>1</v>
+      </c>
+      <c r="F22" t="s">
         <v>38</v>
       </c>
-      <c r="F22">
+      <c r="G22">
         <v>8.99</v>
       </c>
-      <c r="G22">
+      <c r="H22">
         <v>8.49</v>
       </c>
-      <c r="H22" s="2" t="str">
-        <f>_xlfn.XLOOKUP(E22,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
+      <c r="I22" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F22,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
         <v>GCAP2.png</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C23" t="s">
         <v>28</v>
       </c>
-      <c r="C23" t="s">
-        <v>27</v>
-      </c>
-      <c r="D23" s="2">
-        <v>1</v>
-      </c>
-      <c r="E23" t="s">
+      <c r="D23" t="s">
+        <v>27</v>
+      </c>
+      <c r="E23" s="2">
+        <v>1</v>
+      </c>
+      <c r="F23" t="s">
         <v>38</v>
       </c>
-      <c r="F23">
+      <c r="G23">
         <v>8.99</v>
       </c>
-      <c r="G23">
+      <c r="H23">
         <v>8.49</v>
       </c>
-      <c r="H23" s="2" t="str">
-        <f>_xlfn.XLOOKUP(E23,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
+      <c r="I23" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F23,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
         <v>GCAP2.png</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C24" t="s">
         <v>29</v>
       </c>
-      <c r="C24" t="s">
-        <v>27</v>
-      </c>
-      <c r="D24" s="2">
-        <v>1</v>
-      </c>
-      <c r="E24" t="s">
+      <c r="D24" t="s">
+        <v>27</v>
+      </c>
+      <c r="E24" s="2">
+        <v>1</v>
+      </c>
+      <c r="F24" t="s">
         <v>38</v>
       </c>
-      <c r="F24">
+      <c r="G24">
         <v>8.2899999999999991</v>
       </c>
-      <c r="G24">
+      <c r="H24">
         <v>7.7899999999999991</v>
       </c>
-      <c r="H24" s="2" t="str">
-        <f>_xlfn.XLOOKUP(E24,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
+      <c r="I24" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F24,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
         <v>GCAP2.png</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B25" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C25" t="s">
         <v>30</v>
       </c>
-      <c r="C25" t="s">
-        <v>27</v>
-      </c>
-      <c r="D25" s="2">
-        <v>1</v>
-      </c>
-      <c r="E25" t="s">
+      <c r="D25" t="s">
+        <v>27</v>
+      </c>
+      <c r="E25" s="2">
+        <v>1</v>
+      </c>
+      <c r="F25" t="s">
         <v>38</v>
       </c>
-      <c r="F25">
+      <c r="G25">
         <v>8.2899999999999991</v>
       </c>
-      <c r="G25">
+      <c r="H25">
         <v>7.7899999999999991</v>
       </c>
-      <c r="H25" s="2" t="str">
-        <f>_xlfn.XLOOKUP(E25,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
+      <c r="I25" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F25,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
         <v>GCAP2.png</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B26" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C26" t="s">
         <v>31</v>
       </c>
-      <c r="C26" t="s">
-        <v>27</v>
-      </c>
-      <c r="D26" s="2">
-        <v>1</v>
-      </c>
-      <c r="E26" t="s">
+      <c r="D26" t="s">
+        <v>27</v>
+      </c>
+      <c r="E26" s="2">
+        <v>1</v>
+      </c>
+      <c r="F26" t="s">
         <v>38</v>
       </c>
-      <c r="F26">
+      <c r="G26">
         <v>9.49</v>
       </c>
-      <c r="G26">
+      <c r="H26">
         <v>8.99</v>
       </c>
-      <c r="H26" s="2" t="str">
-        <f>_xlfn.XLOOKUP(E26,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
+      <c r="I26" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F26,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
         <v>GCAP2.png</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B27" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C27" t="s">
         <v>4</v>
       </c>
-      <c r="C27" t="s">
-        <v>27</v>
-      </c>
-      <c r="D27" s="2">
-        <v>1</v>
-      </c>
-      <c r="E27" t="s">
+      <c r="D27" t="s">
+        <v>27</v>
+      </c>
+      <c r="E27" s="2">
+        <v>1</v>
+      </c>
+      <c r="F27" t="s">
         <v>39</v>
       </c>
-      <c r="F27">
+      <c r="G27">
         <v>3.49</v>
       </c>
-      <c r="G27">
+      <c r="H27">
         <v>3.1900000000000004</v>
       </c>
-      <c r="H27" s="2" t="str">
-        <f>_xlfn.XLOOKUP(E27,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
+      <c r="I27" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F27,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
         <v>GCA350.png</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B28" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C28" t="s">
         <v>28</v>
       </c>
-      <c r="C28" t="s">
-        <v>27</v>
-      </c>
-      <c r="D28" s="2">
-        <v>1</v>
-      </c>
-      <c r="E28" t="s">
+      <c r="D28" t="s">
+        <v>27</v>
+      </c>
+      <c r="E28" s="2">
+        <v>1</v>
+      </c>
+      <c r="F28" t="s">
         <v>39</v>
       </c>
-      <c r="F28">
+      <c r="G28">
         <v>3.49</v>
       </c>
-      <c r="G28">
+      <c r="H28">
         <v>3.1900000000000004</v>
       </c>
-      <c r="H28" s="2" t="str">
-        <f>_xlfn.XLOOKUP(E28,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
+      <c r="I28" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F28,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
         <v>GCA350.png</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B29" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C29" t="s">
         <v>29</v>
       </c>
-      <c r="C29" t="s">
-        <v>27</v>
-      </c>
-      <c r="D29" s="2">
-        <v>1</v>
-      </c>
-      <c r="E29" t="s">
+      <c r="D29" t="s">
+        <v>27</v>
+      </c>
+      <c r="E29" s="2">
+        <v>1</v>
+      </c>
+      <c r="F29" t="s">
         <v>39</v>
       </c>
-      <c r="F29">
+      <c r="G29">
         <v>3.49</v>
       </c>
-      <c r="G29">
+      <c r="H29">
         <v>3.1900000000000004</v>
       </c>
-      <c r="H29" s="2" t="str">
-        <f>_xlfn.XLOOKUP(E29,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
+      <c r="I29" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F29,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
         <v>GCA350.png</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B30" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C30" t="s">
         <v>30</v>
       </c>
-      <c r="C30" t="s">
-        <v>27</v>
-      </c>
-      <c r="D30" s="2">
-        <v>1</v>
-      </c>
-      <c r="E30" t="s">
+      <c r="D30" t="s">
+        <v>27</v>
+      </c>
+      <c r="E30" s="2">
+        <v>1</v>
+      </c>
+      <c r="F30" t="s">
         <v>39</v>
       </c>
-      <c r="F30">
+      <c r="G30">
         <v>3.49</v>
       </c>
-      <c r="G30">
+      <c r="H30">
         <v>3.1900000000000004</v>
       </c>
-      <c r="H30" s="2" t="str">
-        <f>_xlfn.XLOOKUP(E30,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
+      <c r="I30" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F30,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
         <v>GCA350.png</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B31" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C31" t="s">
         <v>31</v>
       </c>
-      <c r="C31" t="s">
-        <v>27</v>
-      </c>
-      <c r="D31" s="2">
-        <v>1</v>
-      </c>
-      <c r="E31" t="s">
+      <c r="D31" t="s">
+        <v>27</v>
+      </c>
+      <c r="E31" s="2">
+        <v>1</v>
+      </c>
+      <c r="F31" t="s">
         <v>39</v>
       </c>
-      <c r="F31">
+      <c r="G31">
         <v>3.49</v>
       </c>
-      <c r="G31">
+      <c r="H31">
         <v>3.1900000000000004</v>
       </c>
-      <c r="H31" s="2" t="str">
-        <f>_xlfn.XLOOKUP(E31,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
+      <c r="I31" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F31,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
         <v>GCA350.png</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B32" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C32" t="s">
         <v>4</v>
       </c>
-      <c r="C32" t="s">
-        <v>27</v>
-      </c>
-      <c r="D32" s="2">
-        <v>1</v>
-      </c>
-      <c r="E32" t="s">
+      <c r="D32" t="s">
+        <v>27</v>
+      </c>
+      <c r="E32" s="2">
+        <v>1</v>
+      </c>
+      <c r="F32" t="s">
         <v>35</v>
       </c>
-      <c r="F32">
+      <c r="G32">
         <v>5.69</v>
       </c>
-      <c r="G32">
+      <c r="H32">
         <v>5.19</v>
       </c>
-      <c r="H32" s="2" t="str">
-        <f>_xlfn.XLOOKUP(E32,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
+      <c r="I32" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F32,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
         <v>BAREP2.png</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B33" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C33" t="s">
         <v>28</v>
       </c>
-      <c r="C33" t="s">
-        <v>27</v>
-      </c>
-      <c r="D33" s="2">
-        <v>1</v>
-      </c>
-      <c r="E33" t="s">
+      <c r="D33" t="s">
+        <v>27</v>
+      </c>
+      <c r="E33" s="2">
+        <v>1</v>
+      </c>
+      <c r="F33" t="s">
         <v>36</v>
       </c>
-      <c r="F33">
+      <c r="G33">
         <v>5.49</v>
       </c>
-      <c r="G33">
+      <c r="H33">
         <v>5.19</v>
       </c>
-      <c r="H33" s="2" t="str">
-        <f>_xlfn.XLOOKUP(E33,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
+      <c r="I33" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F33,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
         <v>H2OHP500.png</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B34" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C34" t="s">
         <v>29</v>
       </c>
-      <c r="C34" t="s">
-        <v>27</v>
-      </c>
-      <c r="D34" s="2">
-        <v>1</v>
-      </c>
-      <c r="E34" t="s">
+      <c r="D34" t="s">
+        <v>27</v>
+      </c>
+      <c r="E34" s="2">
+        <v>1</v>
+      </c>
+      <c r="F34" t="s">
         <v>36</v>
       </c>
-      <c r="F34">
+      <c r="G34">
         <v>5.49</v>
       </c>
-      <c r="G34">
+      <c r="H34">
         <v>5.19</v>
       </c>
-      <c r="H34" s="2" t="str">
-        <f>_xlfn.XLOOKUP(E34,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
+      <c r="I34" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F34,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
         <v>H2OHP500.png</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B35" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C35" t="s">
         <v>30</v>
       </c>
-      <c r="C35" t="s">
-        <v>27</v>
-      </c>
-      <c r="D35" s="2">
-        <v>1</v>
-      </c>
-      <c r="E35" t="s">
+      <c r="D35" t="s">
+        <v>27</v>
+      </c>
+      <c r="E35" s="2">
+        <v>1</v>
+      </c>
+      <c r="F35" t="s">
         <v>36</v>
       </c>
-      <c r="F35">
+      <c r="G35">
         <v>5.49</v>
       </c>
-      <c r="G35">
+      <c r="H35">
         <v>5.19</v>
       </c>
-      <c r="H35" s="2" t="str">
-        <f>_xlfn.XLOOKUP(E35,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
+      <c r="I35" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F35,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
         <v>H2OHP500.png</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B36" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C36" t="s">
         <v>31</v>
       </c>
-      <c r="C36" t="s">
-        <v>27</v>
-      </c>
-      <c r="D36" s="2">
-        <v>1</v>
-      </c>
-      <c r="E36" t="s">
+      <c r="D36" t="s">
+        <v>27</v>
+      </c>
+      <c r="E36" s="2">
+        <v>1</v>
+      </c>
+      <c r="F36" t="s">
         <v>36</v>
       </c>
-      <c r="F36">
+      <c r="G36">
         <v>5.49</v>
       </c>
-      <c r="G36">
+      <c r="H36">
         <v>5.19</v>
       </c>
-      <c r="H36" s="2" t="str">
-        <f>_xlfn.XLOOKUP(E36,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
+      <c r="I36" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F36,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
         <v>H2OHP500.png</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B37" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C37" t="s">
         <v>4</v>
       </c>
-      <c r="C37" t="s">
-        <v>27</v>
-      </c>
-      <c r="D37" s="2">
-        <v>1</v>
-      </c>
-      <c r="E37" t="s">
+      <c r="D37" t="s">
+        <v>27</v>
+      </c>
+      <c r="E37" s="2">
+        <v>1</v>
+      </c>
+      <c r="F37" t="s">
         <v>40</v>
       </c>
-      <c r="F37">
+      <c r="G37">
         <v>3.39</v>
       </c>
-      <c r="G37">
+      <c r="H37">
         <v>2.99</v>
       </c>
-      <c r="H37" s="2" t="str">
-        <f>_xlfn.XLOOKUP(E37,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
+      <c r="I37" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F37,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
         <v>PCB350.png</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B38" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C38" t="s">
         <v>28</v>
       </c>
-      <c r="C38" t="s">
-        <v>27</v>
-      </c>
-      <c r="D38" s="2">
-        <v>1</v>
-      </c>
-      <c r="E38" t="s">
+      <c r="D38" t="s">
+        <v>27</v>
+      </c>
+      <c r="E38" s="2">
+        <v>1</v>
+      </c>
+      <c r="F38" t="s">
         <v>40</v>
       </c>
-      <c r="F38">
+      <c r="G38">
         <v>3.39</v>
       </c>
-      <c r="G38">
+      <c r="H38">
         <v>2.99</v>
       </c>
-      <c r="H38" s="2" t="str">
-        <f>_xlfn.XLOOKUP(E38,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
+      <c r="I38" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F38,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
         <v>PCB350.png</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B39" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C39" t="s">
         <v>29</v>
       </c>
-      <c r="C39" t="s">
-        <v>27</v>
-      </c>
-      <c r="D39" s="2">
-        <v>1</v>
-      </c>
-      <c r="E39" t="s">
+      <c r="D39" t="s">
+        <v>27</v>
+      </c>
+      <c r="E39" s="2">
+        <v>1</v>
+      </c>
+      <c r="F39" t="s">
         <v>40</v>
       </c>
-      <c r="F39">
+      <c r="G39">
         <v>3.39</v>
       </c>
-      <c r="G39">
+      <c r="H39">
         <v>2.99</v>
       </c>
-      <c r="H39" s="2" t="str">
-        <f>_xlfn.XLOOKUP(E39,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
+      <c r="I39" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F39,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
         <v>PCB350.png</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B40" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C40" t="s">
         <v>30</v>
       </c>
-      <c r="C40" t="s">
-        <v>27</v>
-      </c>
-      <c r="D40" s="2">
-        <v>1</v>
-      </c>
-      <c r="E40" t="s">
+      <c r="D40" t="s">
+        <v>27</v>
+      </c>
+      <c r="E40" s="2">
+        <v>1</v>
+      </c>
+      <c r="F40" t="s">
         <v>40</v>
       </c>
-      <c r="F40">
+      <c r="G40">
         <v>3.39</v>
       </c>
-      <c r="G40">
+      <c r="H40">
         <v>2.99</v>
       </c>
-      <c r="H40" s="2" t="str">
-        <f>_xlfn.XLOOKUP(E40,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
+      <c r="I40" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F40,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
         <v>PCB350.png</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B41" t="s">
+      <c r="B41" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C41" t="s">
         <v>31</v>
       </c>
-      <c r="C41" t="s">
-        <v>27</v>
-      </c>
-      <c r="D41" s="2">
-        <v>1</v>
-      </c>
-      <c r="E41" t="s">
+      <c r="D41" t="s">
+        <v>27</v>
+      </c>
+      <c r="E41" s="2">
+        <v>1</v>
+      </c>
+      <c r="F41" t="s">
         <v>40</v>
       </c>
-      <c r="F41">
+      <c r="G41">
         <v>3.39</v>
       </c>
-      <c r="G41">
+      <c r="H41">
         <v>2.99</v>
       </c>
-      <c r="H41" s="2" t="str">
-        <f>_xlfn.XLOOKUP(E41,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
+      <c r="I41" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F41,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
         <v>PCB350.png</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B42" t="s">
+      <c r="B42" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C42" t="s">
         <v>4</v>
       </c>
-      <c r="C42" t="s">
+      <c r="D42" t="s">
         <v>26</v>
       </c>
-      <c r="D42" s="2">
+      <c r="E42" s="2">
         <v>2</v>
       </c>
-      <c r="E42" t="s">
+      <c r="F42" t="s">
         <v>38</v>
       </c>
-      <c r="F42">
+      <c r="G42">
         <v>8.7899999999999991</v>
       </c>
-      <c r="G42">
+      <c r="H42">
         <v>8.2899999999999991</v>
       </c>
-      <c r="H42" s="2" t="str">
-        <f>_xlfn.XLOOKUP(E42,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
+      <c r="I42" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F42,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
         <v>GCAP2.png</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B43" t="s">
+      <c r="B43" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C43" t="s">
         <v>28</v>
       </c>
-      <c r="C43" t="s">
+      <c r="D43" t="s">
         <v>26</v>
       </c>
-      <c r="D43" s="2">
+      <c r="E43" s="2">
         <v>2</v>
       </c>
-      <c r="E43" t="s">
+      <c r="F43" t="s">
         <v>38</v>
       </c>
-      <c r="F43">
+      <c r="G43">
         <v>8.7899999999999991</v>
       </c>
-      <c r="G43">
+      <c r="H43">
         <v>8.2899999999999991</v>
       </c>
-      <c r="H43" s="2" t="str">
-        <f>_xlfn.XLOOKUP(E43,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
+      <c r="I43" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F43,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
         <v>GCAP2.png</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B44" t="s">
+      <c r="B44" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C44" t="s">
         <v>29</v>
       </c>
-      <c r="C44" t="s">
+      <c r="D44" t="s">
         <v>26</v>
       </c>
-      <c r="D44" s="2">
+      <c r="E44" s="2">
         <v>2</v>
       </c>
-      <c r="E44" t="s">
+      <c r="F44" t="s">
         <v>38</v>
       </c>
-      <c r="F44">
+      <c r="G44">
         <v>7.99</v>
       </c>
-      <c r="G44">
+      <c r="H44">
         <v>7.49</v>
       </c>
-      <c r="H44" s="2" t="str">
-        <f>_xlfn.XLOOKUP(E44,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
+      <c r="I44" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F44,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
         <v>GCAP2.png</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B45" t="s">
+      <c r="B45" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C45" t="s">
         <v>30</v>
       </c>
-      <c r="C45" t="s">
+      <c r="D45" t="s">
         <v>26</v>
       </c>
-      <c r="D45" s="2">
+      <c r="E45" s="2">
         <v>2</v>
       </c>
-      <c r="E45" t="s">
+      <c r="F45" t="s">
         <v>38</v>
       </c>
-      <c r="F45">
+      <c r="G45">
         <v>7.99</v>
       </c>
-      <c r="G45">
+      <c r="H45">
         <v>7.49</v>
       </c>
-      <c r="H45" s="2" t="str">
-        <f>_xlfn.XLOOKUP(E45,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
+      <c r="I45" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F45,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
         <v>GCAP2.png</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B46" t="s">
+      <c r="B46" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C46" t="s">
         <v>31</v>
       </c>
-      <c r="C46" t="s">
+      <c r="D46" t="s">
         <v>26</v>
       </c>
-      <c r="D46" s="2">
+      <c r="E46" s="2">
         <v>2</v>
       </c>
-      <c r="E46" t="s">
+      <c r="F46" t="s">
         <v>38</v>
       </c>
-      <c r="F46">
+      <c r="G46">
         <v>9.2899999999999991</v>
       </c>
-      <c r="G46">
+      <c r="H46">
         <v>8.7899999999999991</v>
       </c>
-      <c r="H46" s="2" t="str">
-        <f>_xlfn.XLOOKUP(E46,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
+      <c r="I46" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F46,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
         <v>GCAP2.png</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B47" t="s">
+      <c r="B47" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C47" t="s">
         <v>4</v>
       </c>
-      <c r="C47" t="s">
+      <c r="D47" t="s">
         <v>26</v>
       </c>
-      <c r="D47" s="2">
+      <c r="E47" s="2">
         <v>2</v>
       </c>
-      <c r="E47" t="s">
+      <c r="F47" t="s">
         <v>41</v>
       </c>
-      <c r="F47">
+      <c r="G47">
         <v>2.39</v>
       </c>
-      <c r="G47">
+      <c r="H47">
         <v>2.19</v>
       </c>
-      <c r="H47" s="2" t="str">
-        <f>_xlfn.XLOOKUP(E47,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
+      <c r="I47" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F47,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
         <v>GCA269.png</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B48" t="s">
+      <c r="B48" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C48" t="s">
         <v>28</v>
       </c>
-      <c r="C48" t="s">
+      <c r="D48" t="s">
         <v>26</v>
       </c>
-      <c r="D48" s="2">
+      <c r="E48" s="2">
         <v>2</v>
       </c>
-      <c r="E48" t="s">
+      <c r="F48" t="s">
         <v>41</v>
       </c>
-      <c r="F48">
+      <c r="G48">
         <v>2.39</v>
       </c>
-      <c r="G48">
+      <c r="H48">
         <v>2.19</v>
       </c>
-      <c r="H48" s="2" t="str">
-        <f>_xlfn.XLOOKUP(E48,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
+      <c r="I48" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F48,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
         <v>GCA269.png</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B49" t="s">
+      <c r="B49" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C49" t="s">
         <v>29</v>
       </c>
-      <c r="C49" t="s">
+      <c r="D49" t="s">
         <v>26</v>
       </c>
-      <c r="D49" s="2">
+      <c r="E49" s="2">
         <v>2</v>
       </c>
-      <c r="E49" t="s">
+      <c r="F49" t="s">
         <v>41</v>
       </c>
-      <c r="F49">
+      <c r="G49">
         <v>2.39</v>
       </c>
-      <c r="G49">
+      <c r="H49">
         <v>2.19</v>
       </c>
-      <c r="H49" s="2" t="str">
-        <f>_xlfn.XLOOKUP(E49,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
+      <c r="I49" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F49,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
         <v>GCA269.png</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B50" t="s">
+      <c r="B50" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C50" t="s">
         <v>30</v>
       </c>
-      <c r="C50" t="s">
+      <c r="D50" t="s">
         <v>26</v>
       </c>
-      <c r="D50" s="2">
+      <c r="E50" s="2">
         <v>2</v>
       </c>
-      <c r="E50" t="s">
+      <c r="F50" t="s">
         <v>41</v>
       </c>
-      <c r="F50">
+      <c r="G50">
         <v>2.39</v>
       </c>
-      <c r="G50">
+      <c r="H50">
         <v>2.19</v>
       </c>
-      <c r="H50" s="2" t="str">
-        <f>_xlfn.XLOOKUP(E50,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
+      <c r="I50" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F50,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
         <v>GCA269.png</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B51" t="s">
+      <c r="B51" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C51" t="s">
         <v>31</v>
       </c>
-      <c r="C51" t="s">
+      <c r="D51" t="s">
         <v>26</v>
       </c>
-      <c r="D51" s="2">
+      <c r="E51" s="2">
         <v>2</v>
       </c>
-      <c r="E51" t="s">
+      <c r="F51" t="s">
         <v>41</v>
       </c>
-      <c r="F51">
+      <c r="G51">
         <v>2.39</v>
       </c>
-      <c r="G51">
+      <c r="H51">
         <v>2.19</v>
       </c>
-      <c r="H51" s="2" t="str">
-        <f>_xlfn.XLOOKUP(E51,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
+      <c r="I51" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F51,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
         <v>GCA269.png</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B52" t="s">
+      <c r="B52" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C52" t="s">
         <v>4</v>
       </c>
-      <c r="C52" t="s">
+      <c r="D52" t="s">
         <v>26</v>
       </c>
-      <c r="D52" s="2">
+      <c r="E52" s="2">
         <v>2</v>
       </c>
-      <c r="E52" t="s">
+      <c r="F52" t="s">
         <v>42</v>
       </c>
-      <c r="F52">
+      <c r="G52">
         <v>2.29</v>
       </c>
-      <c r="G52">
+      <c r="H52">
         <v>2.09</v>
       </c>
-      <c r="H52" s="2" t="str">
-        <f>_xlfn.XLOOKUP(E52,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
+      <c r="I52" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F52,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
         <v>PC269.png</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B53" t="s">
+      <c r="B53" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C53" t="s">
         <v>28</v>
       </c>
-      <c r="C53" t="s">
+      <c r="D53" t="s">
         <v>26</v>
       </c>
-      <c r="D53" s="2">
+      <c r="E53" s="2">
         <v>2</v>
       </c>
-      <c r="E53" t="s">
+      <c r="F53" t="s">
         <v>42</v>
       </c>
-      <c r="F53">
+      <c r="G53">
         <v>2.29</v>
       </c>
-      <c r="G53">
+      <c r="H53">
         <v>2.09</v>
       </c>
-      <c r="H53" s="2" t="str">
-        <f>_xlfn.XLOOKUP(E53,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
+      <c r="I53" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F53,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
         <v>PC269.png</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B54" t="s">
+      <c r="B54" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C54" t="s">
         <v>29</v>
       </c>
-      <c r="C54" t="s">
+      <c r="D54" t="s">
         <v>26</v>
       </c>
-      <c r="D54" s="2">
+      <c r="E54" s="2">
         <v>2</v>
       </c>
-      <c r="E54" t="s">
+      <c r="F54" t="s">
         <v>42</v>
       </c>
-      <c r="F54">
+      <c r="G54">
         <v>2.29</v>
       </c>
-      <c r="G54">
+      <c r="H54">
         <v>2.09</v>
       </c>
-      <c r="H54" s="2" t="str">
-        <f>_xlfn.XLOOKUP(E54,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
+      <c r="I54" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F54,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
         <v>PC269.png</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B55" t="s">
+      <c r="B55" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C55" t="s">
         <v>30</v>
       </c>
-      <c r="C55" t="s">
+      <c r="D55" t="s">
         <v>26</v>
       </c>
-      <c r="D55" s="2">
+      <c r="E55" s="2">
         <v>2</v>
       </c>
-      <c r="E55" t="s">
+      <c r="F55" t="s">
         <v>42</v>
       </c>
-      <c r="F55">
+      <c r="G55">
         <v>2.29</v>
       </c>
-      <c r="G55">
+      <c r="H55">
         <v>2.09</v>
       </c>
-      <c r="H55" s="2" t="str">
-        <f>_xlfn.XLOOKUP(E55,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
+      <c r="I55" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F55,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
         <v>PC269.png</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B56" t="s">
+      <c r="B56" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C56" t="s">
         <v>31</v>
       </c>
-      <c r="C56" t="s">
+      <c r="D56" t="s">
         <v>26</v>
       </c>
-      <c r="D56" s="2">
+      <c r="E56" s="2">
         <v>2</v>
       </c>
-      <c r="E56" t="s">
+      <c r="F56" t="s">
         <v>42</v>
       </c>
-      <c r="F56">
+      <c r="G56">
         <v>2.29</v>
       </c>
-      <c r="G56">
+      <c r="H56">
         <v>2.09</v>
       </c>
-      <c r="H56" s="2" t="str">
-        <f>_xlfn.XLOOKUP(E56,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
+      <c r="I56" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F56,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
         <v>PC269.png</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B57" t="s">
+      <c r="B57" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C57" t="s">
         <v>4</v>
       </c>
-      <c r="C57" t="s">
-        <v>27</v>
-      </c>
-      <c r="D57" s="2">
+      <c r="D57" t="s">
+        <v>27</v>
+      </c>
+      <c r="E57" s="2">
         <v>2</v>
       </c>
-      <c r="E57" t="s">
+      <c r="F57" t="s">
         <v>32</v>
       </c>
-      <c r="F57">
+      <c r="G57">
         <v>5.29</v>
       </c>
-      <c r="G57">
+      <c r="H57">
         <v>4.99</v>
       </c>
-      <c r="H57" s="2" t="str">
-        <f>_xlfn.XLOOKUP(E57,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
+      <c r="I57" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F57,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
         <v>GCAP1.png</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B58" t="s">
+      <c r="B58" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C58" t="s">
         <v>28</v>
       </c>
-      <c r="C58" t="s">
-        <v>27</v>
-      </c>
-      <c r="D58" s="2">
+      <c r="D58" t="s">
+        <v>27</v>
+      </c>
+      <c r="E58" s="2">
         <v>2</v>
       </c>
-      <c r="E58" t="s">
+      <c r="F58" t="s">
         <v>33</v>
       </c>
-      <c r="F58">
+      <c r="G58">
         <v>6.99</v>
       </c>
-      <c r="G58">
+      <c r="H58">
         <v>6.69</v>
       </c>
-      <c r="H58" s="2" t="str">
-        <f>_xlfn.XLOOKUP(E58,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
+      <c r="I58" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F58,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
         <v>GCAP1,5.png</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B59" t="s">
+      <c r="B59" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C59" t="s">
         <v>29</v>
       </c>
-      <c r="C59" t="s">
-        <v>27</v>
-      </c>
-      <c r="D59" s="2">
+      <c r="D59" t="s">
+        <v>27</v>
+      </c>
+      <c r="E59" s="2">
         <v>2</v>
       </c>
-      <c r="E59" t="s">
+      <c r="F59" t="s">
         <v>33</v>
       </c>
-      <c r="F59">
+      <c r="G59">
         <v>6.99</v>
       </c>
-      <c r="G59">
+      <c r="H59">
         <v>6.69</v>
       </c>
-      <c r="H59" s="2" t="str">
-        <f>_xlfn.XLOOKUP(E59,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
+      <c r="I59" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F59,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
         <v>GCAP1,5.png</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B60" t="s">
+      <c r="B60" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C60" t="s">
         <v>30</v>
       </c>
-      <c r="C60" t="s">
-        <v>27</v>
-      </c>
-      <c r="D60" s="2">
+      <c r="D60" t="s">
+        <v>27</v>
+      </c>
+      <c r="E60" s="2">
         <v>2</v>
       </c>
-      <c r="E60" t="s">
+      <c r="F60" t="s">
         <v>33</v>
       </c>
-      <c r="F60">
+      <c r="G60">
         <v>6.99</v>
       </c>
-      <c r="G60">
+      <c r="H60">
         <v>6.69</v>
       </c>
-      <c r="H60" s="2" t="str">
-        <f>_xlfn.XLOOKUP(E60,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
+      <c r="I60" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F60,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
         <v>GCAP1,5.png</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B61" t="s">
+      <c r="B61" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C61" t="s">
         <v>31</v>
       </c>
-      <c r="C61" t="s">
-        <v>27</v>
-      </c>
-      <c r="D61" s="2">
+      <c r="D61" t="s">
+        <v>27</v>
+      </c>
+      <c r="E61" s="2">
         <v>2</v>
       </c>
-      <c r="E61" t="s">
+      <c r="F61" t="s">
         <v>33</v>
       </c>
-      <c r="F61">
+      <c r="G61">
         <v>6.99</v>
       </c>
-      <c r="G61">
+      <c r="H61">
         <v>6.69</v>
       </c>
-      <c r="H61" s="2" t="str">
-        <f>_xlfn.XLOOKUP(E61,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
+      <c r="I61" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F61,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
         <v>GCAP1,5.png</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B62" t="s">
+      <c r="B62" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C62" t="s">
         <v>4</v>
       </c>
-      <c r="C62" t="s">
-        <v>27</v>
-      </c>
-      <c r="D62" s="2">
+      <c r="D62" t="s">
+        <v>27</v>
+      </c>
+      <c r="E62" s="2">
         <v>2</v>
       </c>
-      <c r="E62" t="s">
+      <c r="F62" t="s">
         <v>34</v>
       </c>
-      <c r="F62">
+      <c r="G62">
         <v>7.99</v>
       </c>
-      <c r="G62">
+      <c r="H62">
         <v>7.49</v>
       </c>
-      <c r="H62" s="2" t="str">
-        <f>_xlfn.XLOOKUP(E62,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
+      <c r="I62" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F62,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
         <v>PCP2.png</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B63" t="s">
+      <c r="B63" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C63" t="s">
         <v>28</v>
       </c>
-      <c r="C63" t="s">
-        <v>27</v>
-      </c>
-      <c r="D63" s="2">
+      <c r="D63" t="s">
+        <v>27</v>
+      </c>
+      <c r="E63" s="2">
         <v>2</v>
       </c>
-      <c r="E63" t="s">
+      <c r="F63" t="s">
         <v>34</v>
       </c>
-      <c r="F63">
+      <c r="G63">
         <v>8.49</v>
       </c>
-      <c r="G63">
+      <c r="H63">
         <v>7.99</v>
       </c>
-      <c r="H63" s="2" t="str">
-        <f>_xlfn.XLOOKUP(E63,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
+      <c r="I63" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F63,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
         <v>PCP2.png</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B64" t="s">
+      <c r="B64" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C64" t="s">
         <v>29</v>
       </c>
-      <c r="C64" t="s">
-        <v>27</v>
-      </c>
-      <c r="D64" s="2">
+      <c r="D64" t="s">
+        <v>27</v>
+      </c>
+      <c r="E64" s="2">
         <v>2</v>
       </c>
-      <c r="E64" t="s">
+      <c r="F64" t="s">
         <v>34</v>
       </c>
-      <c r="F64">
+      <c r="G64">
         <v>7.69</v>
       </c>
-      <c r="G64">
+      <c r="H64">
         <v>7.19</v>
       </c>
-      <c r="H64" s="2" t="str">
-        <f>_xlfn.XLOOKUP(E64,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
+      <c r="I64" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F64,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
         <v>PCP2.png</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B65" t="s">
+      <c r="B65" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C65" t="s">
         <v>30</v>
       </c>
-      <c r="C65" t="s">
-        <v>27</v>
-      </c>
-      <c r="D65" s="2">
+      <c r="D65" t="s">
+        <v>27</v>
+      </c>
+      <c r="E65" s="2">
         <v>2</v>
       </c>
-      <c r="E65" t="s">
+      <c r="F65" t="s">
         <v>34</v>
       </c>
-      <c r="F65">
+      <c r="G65">
         <v>7.69</v>
       </c>
-      <c r="G65">
+      <c r="H65">
         <v>7.19</v>
       </c>
-      <c r="H65" s="2" t="str">
-        <f>_xlfn.XLOOKUP(E65,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
+      <c r="I65" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F65,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
         <v>PCP2.png</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B66" t="s">
+      <c r="B66" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C66" t="s">
         <v>31</v>
       </c>
-      <c r="C66" t="s">
-        <v>27</v>
-      </c>
-      <c r="D66" s="2">
+      <c r="D66" t="s">
+        <v>27</v>
+      </c>
+      <c r="E66" s="2">
         <v>2</v>
       </c>
-      <c r="E66" t="s">
+      <c r="F66" t="s">
         <v>34</v>
       </c>
-      <c r="F66">
+      <c r="G66">
         <v>8.49</v>
       </c>
-      <c r="G66">
+      <c r="H66">
         <v>7.99</v>
       </c>
-      <c r="H66" s="2" t="str">
-        <f>_xlfn.XLOOKUP(E66,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
+      <c r="I66" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F66,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
         <v>PCP2.png</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B67" t="s">
+      <c r="B67" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C67" t="s">
         <v>28</v>
       </c>
-      <c r="C67" t="s">
-        <v>27</v>
-      </c>
-      <c r="D67" s="2">
+      <c r="D67" t="s">
+        <v>27</v>
+      </c>
+      <c r="E67" s="2">
         <v>2</v>
       </c>
-      <c r="E67" t="s">
+      <c r="F67" t="s">
         <v>43</v>
       </c>
-      <c r="F67">
+      <c r="G67">
         <v>8.49</v>
       </c>
-      <c r="G67">
+      <c r="H67">
         <v>7.99</v>
       </c>
-      <c r="H67" s="2" t="str">
-        <f>_xlfn.XLOOKUP(E67,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
+      <c r="I67" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F67,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
         <v>H2OHP1,5.png</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B68" t="s">
+      <c r="B68" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C68" t="s">
         <v>29</v>
       </c>
-      <c r="C68" t="s">
-        <v>27</v>
-      </c>
-      <c r="D68" s="2">
+      <c r="D68" t="s">
+        <v>27</v>
+      </c>
+      <c r="E68" s="2">
         <v>2</v>
       </c>
-      <c r="E68" t="s">
+      <c r="F68" t="s">
         <v>43</v>
       </c>
-      <c r="F68">
+      <c r="G68">
         <v>7.99</v>
       </c>
-      <c r="G68">
+      <c r="H68">
         <v>7.49</v>
       </c>
-      <c r="H68" s="2" t="str">
-        <f>_xlfn.XLOOKUP(E68,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
+      <c r="I68" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F68,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
         <v>H2OHP1,5.png</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B69" t="s">
+      <c r="B69" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C69" t="s">
         <v>30</v>
       </c>
-      <c r="C69" t="s">
-        <v>27</v>
-      </c>
-      <c r="D69" s="2">
+      <c r="D69" t="s">
+        <v>27</v>
+      </c>
+      <c r="E69" s="2">
         <v>2</v>
       </c>
-      <c r="E69" t="s">
+      <c r="F69" t="s">
         <v>43</v>
       </c>
-      <c r="F69">
+      <c r="G69">
         <v>7.99</v>
       </c>
-      <c r="G69">
+      <c r="H69">
         <v>7.49</v>
       </c>
-      <c r="H69" s="2" t="str">
-        <f>_xlfn.XLOOKUP(E69,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
+      <c r="I69" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F69,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
         <v>H2OHP1,5.png</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B70" t="s">
+      <c r="B70" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C70" t="s">
         <v>31</v>
       </c>
-      <c r="C70" t="s">
-        <v>27</v>
-      </c>
-      <c r="D70" s="2">
+      <c r="D70" t="s">
+        <v>27</v>
+      </c>
+      <c r="E70" s="2">
         <v>2</v>
       </c>
-      <c r="E70" t="s">
+      <c r="F70" t="s">
         <v>43</v>
       </c>
-      <c r="F70">
+      <c r="G70">
         <v>8.49</v>
       </c>
-      <c r="G70">
+      <c r="H70">
         <v>7.99</v>
       </c>
-      <c r="H70" s="2" t="str">
-        <f>_xlfn.XLOOKUP(E70,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
+      <c r="I70" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F70,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
         <v>H2OHP1,5.png</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B71" t="s">
+      <c r="B71" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C71" t="s">
         <v>4</v>
       </c>
-      <c r="C71" t="s">
-        <v>27</v>
-      </c>
-      <c r="D71" s="2">
+      <c r="D71" t="s">
+        <v>27</v>
+      </c>
+      <c r="E71" s="2">
         <v>2</v>
       </c>
-      <c r="E71" t="s">
+      <c r="F71" t="s">
         <v>37</v>
       </c>
-      <c r="F71">
+      <c r="G71">
         <v>6.99</v>
       </c>
-      <c r="G71">
+      <c r="H71">
         <v>6.49</v>
       </c>
-      <c r="H71" s="2" t="str">
-        <f>_xlfn.XLOOKUP(E71,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
+      <c r="I71" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F71,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
         <v>SUKP2.png</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B72" t="s">
+      <c r="B72" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C72" t="s">
         <v>28</v>
       </c>
-      <c r="C72" t="s">
-        <v>27</v>
-      </c>
-      <c r="D72" s="2">
+      <c r="D72" t="s">
+        <v>27</v>
+      </c>
+      <c r="E72" s="2">
         <v>2</v>
       </c>
-      <c r="E72" t="s">
+      <c r="F72" t="s">
         <v>37</v>
       </c>
-      <c r="F72">
+      <c r="G72">
         <v>6.99</v>
       </c>
-      <c r="G72">
+      <c r="H72">
         <v>6.49</v>
       </c>
-      <c r="H72" s="2" t="str">
-        <f>_xlfn.XLOOKUP(E72,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
+      <c r="I72" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F72,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
         <v>SUKP2.png</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B73" t="s">
+      <c r="B73" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C73" t="s">
         <v>29</v>
       </c>
-      <c r="C73" t="s">
-        <v>27</v>
-      </c>
-      <c r="D73" s="2">
+      <c r="D73" t="s">
+        <v>27</v>
+      </c>
+      <c r="E73" s="2">
         <v>2</v>
       </c>
-      <c r="E73" t="s">
+      <c r="F73" t="s">
         <v>37</v>
       </c>
-      <c r="F73">
+      <c r="G73">
         <v>6.99</v>
       </c>
-      <c r="G73">
+      <c r="H73">
         <v>6.49</v>
       </c>
-      <c r="H73" s="2" t="str">
-        <f>_xlfn.XLOOKUP(E73,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
+      <c r="I73" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F73,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
         <v>SUKP2.png</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B74" t="s">
+      <c r="B74" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C74" t="s">
         <v>30</v>
       </c>
-      <c r="C74" t="s">
-        <v>27</v>
-      </c>
-      <c r="D74" s="2">
+      <c r="D74" t="s">
+        <v>27</v>
+      </c>
+      <c r="E74" s="2">
         <v>2</v>
       </c>
-      <c r="E74" t="s">
+      <c r="F74" t="s">
         <v>37</v>
       </c>
-      <c r="F74">
+      <c r="G74">
         <v>6.99</v>
       </c>
-      <c r="G74">
+      <c r="H74">
         <v>6.49</v>
       </c>
-      <c r="H74" s="2" t="str">
-        <f>_xlfn.XLOOKUP(E74,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
+      <c r="I74" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F74,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
         <v>SUKP2.png</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B75" t="s">
+      <c r="B75" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C75" t="s">
         <v>31</v>
       </c>
-      <c r="C75" t="s">
-        <v>27</v>
-      </c>
-      <c r="D75" s="2">
+      <c r="D75" t="s">
+        <v>27</v>
+      </c>
+      <c r="E75" s="2">
         <v>2</v>
       </c>
-      <c r="E75" t="s">
+      <c r="F75" t="s">
         <v>37</v>
       </c>
-      <c r="F75">
+      <c r="G75">
         <v>7.49</v>
       </c>
-      <c r="G75">
+      <c r="H75">
         <v>6.99</v>
       </c>
-      <c r="H75" s="2" t="str">
-        <f>_xlfn.XLOOKUP(E75,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
+      <c r="I75" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F75,DeparaIMG!A:A,DeparaIMG!C:C,,0)</f>
         <v>SUKP2.png</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="D76" s="2"/>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="E76" s="2"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H75" xr:uid="{34B2C8DF-4561-40B2-8E7C-6CD69559B9AE}"/>
+  <autoFilter ref="A1:I75" xr:uid="{34B2C8DF-4561-40B2-8E7C-6CD69559B9AE}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>

--- a/data/calendario_promocional.xlsx
+++ b/data/calendario_promocional.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://anheuserbuschinbev-my.sharepoint.com/personal/99823517_ab-inbev_com/Documents/001. Projetos/Streamlit Calendario/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="360" documentId="11_F25DC773A252ABDACC1048AAA9DA54025ADE5901" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2D11228F-D49C-4E13-B53F-AD32E22B799A}"/>
+  <xr:revisionPtr revIDLastSave="379" documentId="11_F25DC773A252ABDACC1048AAA9DA54025ADE5901" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{89CBF855-3242-4F60-8101-47E1BAB69DB6}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DeparaIMG" sheetId="5" r:id="rId1"/>
@@ -20,6 +20,7 @@
     <sheet name="CONFIG" sheetId="4" r:id="rId5"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">CALENDARIO!$A$1:$B$53</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">DeparaIMG!$A$1:$D$37</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">PRODUTOS!$A$1:$I$496</definedName>
   </definedNames>
@@ -44,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2743" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2789" uniqueCount="108">
   <si>
     <t>Data</t>
   </si>
@@ -1307,7 +1308,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B35"/>
+  <dimension ref="A1:B53"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
@@ -1341,7 +1342,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
-        <f t="shared" ref="A4:A35" si="0">A3+1</f>
+        <f t="shared" ref="A4:A53" si="0">A3+1</f>
         <v>46268</v>
       </c>
       <c r="B4" s="2" t="s">
@@ -1566,75 +1567,237 @@
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="3">
-        <f t="shared" si="0"/>
-        <v>46293</v>
+        <v>46296</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" s="3">
         <f t="shared" si="0"/>
-        <v>46294</v>
+        <v>46297</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" s="3">
         <f t="shared" si="0"/>
-        <v>46295</v>
+        <v>46298</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" s="3">
         <f t="shared" si="0"/>
-        <v>46296</v>
+        <v>46299</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" s="3">
         <f t="shared" si="0"/>
-        <v>46297</v>
+        <v>46300</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" s="3">
         <f t="shared" si="0"/>
-        <v>46298</v>
+        <v>46301</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" s="3">
         <f t="shared" si="0"/>
-        <v>46299</v>
+        <v>46302</v>
       </c>
       <c r="B35" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" s="3">
+        <f t="shared" si="0"/>
+        <v>46303</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" s="3">
+        <f t="shared" si="0"/>
+        <v>46304</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" s="3">
+        <f t="shared" si="0"/>
+        <v>46305</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" s="3">
+        <f t="shared" si="0"/>
+        <v>46306</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" s="3">
+        <f t="shared" si="0"/>
+        <v>46307</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41" s="3">
+        <f t="shared" si="0"/>
+        <v>46308</v>
+      </c>
+      <c r="B41" s="2" t="s">
         <v>22</v>
       </c>
     </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42" s="3">
+        <f t="shared" si="0"/>
+        <v>46309</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A43" s="3">
+        <f t="shared" si="0"/>
+        <v>46310</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A44" s="3">
+        <f t="shared" si="0"/>
+        <v>46311</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A45" s="3">
+        <f t="shared" si="0"/>
+        <v>46312</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A46" s="3">
+        <f t="shared" si="0"/>
+        <v>46313</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A47" s="3">
+        <f t="shared" si="0"/>
+        <v>46314</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A48" s="3">
+        <f t="shared" si="0"/>
+        <v>46315</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A49" s="3">
+        <f t="shared" si="0"/>
+        <v>46316</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A50" s="3">
+        <f t="shared" si="0"/>
+        <v>46317</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A51" s="3">
+        <f t="shared" si="0"/>
+        <v>46318</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A52" s="3">
+        <f t="shared" si="0"/>
+        <v>46319</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A53" s="3">
+        <f t="shared" si="0"/>
+        <v>46320</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A1:B53" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D40F4A5-E774-499A-A01D-1C21EEE25028}">
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="4" max="4" width="47.5703125" bestFit="1" customWidth="1"/>
@@ -1834,6 +1997,104 @@
       </c>
       <c r="D14" s="2" t="s">
         <v>102</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>62</v>
       </c>
     </row>
   </sheetData>

--- a/data/calendario_promocional.xlsx
+++ b/data/calendario_promocional.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://anheuserbuschinbev-my.sharepoint.com/personal/99823517_ab-inbev_com/Documents/001. Projetos/Streamlit Calendario/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="379" documentId="11_F25DC773A252ABDACC1048AAA9DA54025ADE5901" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{89CBF855-3242-4F60-8101-47E1BAB69DB6}"/>
+  <xr:revisionPtr revIDLastSave="398" documentId="11_F25DC773A252ABDACC1048AAA9DA54025ADE5901" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C6AB7BFD-83AD-4805-B0E6-75032F122FF5}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DeparaIMG" sheetId="5" r:id="rId1"/>
@@ -15119,10 +15119,10 @@
         <v>33</v>
       </c>
       <c r="G434">
-        <v>6.79</v>
+        <v>5.99</v>
       </c>
       <c r="H434">
-        <v>6.39</v>
+        <v>5.59</v>
       </c>
       <c r="I434" s="2" t="str">
         <f>_xlfn.XLOOKUP(F434,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
@@ -15149,10 +15149,10 @@
         <v>33</v>
       </c>
       <c r="G435">
-        <v>6.49</v>
+        <v>5.99</v>
       </c>
       <c r="H435">
-        <v>6.09</v>
+        <v>5.59</v>
       </c>
       <c r="I435" s="2" t="str">
         <f>_xlfn.XLOOKUP(F435,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
@@ -15179,10 +15179,10 @@
         <v>33</v>
       </c>
       <c r="G436">
-        <v>6.49</v>
+        <v>5.99</v>
       </c>
       <c r="H436">
-        <v>6.09</v>
+        <v>5.59</v>
       </c>
       <c r="I436" s="2" t="str">
         <f>_xlfn.XLOOKUP(F436,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
@@ -15209,10 +15209,10 @@
         <v>33</v>
       </c>
       <c r="G437">
-        <v>6.99</v>
+        <v>5.99</v>
       </c>
       <c r="H437">
-        <v>6.59</v>
+        <v>5.59</v>
       </c>
       <c r="I437" s="2" t="str">
         <f>_xlfn.XLOOKUP(F437,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
